--- a/exemplo/quadro-de-cargas-residencia-unifamiliar-exemplo-r00.xlsx
+++ b/exemplo/quadro-de-cargas-residencia-unifamiliar-exemplo-r00.xlsx
@@ -28,7 +28,7 @@
     <t>Obra: Residência unifamiliar — exemplo — Proprietário (exemplo)</t>
   </si>
   <si>
-    <t>Sistema: 127/220 V, trifásico, esquema TN-S · Responsável: Nome do responsável técnico — CREA/CFT nº 000000 · R00 · 17/10/2026</t>
+    <t>Sistema: 127/220 V, trifásico, esquema TN-S · Responsável: Nome do responsável técnico — CREA/CFT nº 000000 · R00 · 20/10/2026</t>
   </si>
   <si>
     <t>Circ.</t>

--- a/exemplo/quadro-de-cargas-residencia-unifamiliar-exemplo-r00.xlsx
+++ b/exemplo/quadro-de-cargas-residencia-unifamiliar-exemplo-r00.xlsx
@@ -14,13 +14,14 @@
     <sheet sheetId="8" name="Cargas Energisa" state="visible" r:id="rId11"/>
     <sheet sheetId="9" name="Carga térmica" state="visible" r:id="rId12"/>
     <sheet sheetId="10" name="Perfil horário" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Lista de materiais" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="423">
   <si>
     <t>Quadro de cargas — QM — Quadro de medição (ponto de entrega)</t>
   </si>
@@ -917,16 +918,389 @@
   </si>
   <si>
     <t>Simultânea (W)</t>
+  </si>
+  <si>
+    <t>Lista de materiais</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Descrição / especificação</t>
+  </si>
+  <si>
+    <t>Norma de fabricação</t>
+  </si>
+  <si>
+    <t>Fabricante / ref.</t>
+  </si>
+  <si>
+    <t>Unid.</t>
+  </si>
+  <si>
+    <t>Origem</t>
+  </si>
+  <si>
+    <t>Padrão de entrada</t>
+  </si>
+  <si>
+    <t>Caixa de medição CMI-02 — padrão Energisa (NDU 001), categoria T3</t>
+  </si>
+  <si>
+    <t>Energisa NDU 001</t>
+  </si>
+  <si>
+    <t>un</t>
+  </si>
+  <si>
+    <t>Disjuntor termomagnético geral 3P 70 A — proteção do padrão de entrada</t>
+  </si>
+  <si>
+    <t>ABNT NBR NM 60898 / NBR IEC 60947-2</t>
+  </si>
+  <si>
+    <t>Ramal de entrada: cobre 0,6/1 kV, isolação XLPE/HEPR/EPR 90 °C, embutido: fase 16 mm² e neutro 16 mm²</t>
+  </si>
+  <si>
+    <t>vb</t>
+  </si>
+  <si>
+    <t>Eletroduto do ramal de entrada 1 1/4"</t>
+  </si>
+  <si>
+    <t>Condutores e cabos</t>
+  </si>
+  <si>
+    <t>Condutor isolado 450/750 V, cobre classe 5, PVC 70 °C — 1,5 mm², cor preto (fase)</t>
+  </si>
+  <si>
+    <t>ABNT NBR NM 247-3</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>1, 11</t>
+  </si>
+  <si>
+    <t>Condutor isolado 450/750 V, cobre classe 5, PVC 70 °C — 1,5 mm², cor vermelho (fase)</t>
+  </si>
+  <si>
+    <t>Condutor isolado 450/750 V, cobre classe 5, PVC 70 °C — 1,5 mm², cor azul-claro (neutro)</t>
+  </si>
+  <si>
+    <t>1, 2, 11</t>
+  </si>
+  <si>
+    <t>Condutor isolado 450/750 V, cobre classe 5, PVC 70 °C — 1,5 mm², cor verde-amarelo (proteção)</t>
+  </si>
+  <si>
+    <t>Condutor isolado 450/750 V, cobre classe 5, PVC 70 °C — 2,5 mm², cor preto (fase)</t>
+  </si>
+  <si>
+    <t>Condutor isolado 450/750 V, cobre classe 5, PVC 70 °C — 2,5 mm², cor vermelho (fase)</t>
+  </si>
+  <si>
+    <t>Condutor isolado 450/750 V, cobre classe 5, PVC 70 °C — 2,5 mm², cor branco (fase)</t>
+  </si>
+  <si>
+    <t>3, 8</t>
+  </si>
+  <si>
+    <t>Condutor isolado 450/750 V, cobre classe 5, PVC 70 °C — 2,5 mm², cor azul-claro (neutro)</t>
+  </si>
+  <si>
+    <t>3, 12</t>
+  </si>
+  <si>
+    <t>Condutor isolado 450/750 V, cobre classe 5, PVC 70 °C — 2,5 mm², cor verde-amarelo (proteção)</t>
+  </si>
+  <si>
+    <t>3, 8, 12</t>
+  </si>
+  <si>
+    <t>Condutor isolado 450/750 V, cobre classe 5, PVC 70 °C — 4 mm², cor preto (fase)</t>
+  </si>
+  <si>
+    <t>4, 6</t>
+  </si>
+  <si>
+    <t>Condutor isolado 450/750 V, cobre classe 5, PVC 70 °C — 4 mm², cor vermelho (fase)</t>
+  </si>
+  <si>
+    <t>5, 6</t>
+  </si>
+  <si>
+    <t>Condutor isolado 450/750 V, cobre classe 5, PVC 70 °C — 4 mm², cor branco (fase)</t>
+  </si>
+  <si>
+    <t>Condutor isolado 450/750 V, cobre classe 5, PVC 70 °C — 4 mm², cor azul-claro (neutro)</t>
+  </si>
+  <si>
+    <t>4, 5, 9</t>
+  </si>
+  <si>
+    <t>Condutor isolado 450/750 V, cobre classe 5, PVC 70 °C — 4 mm², cor verde-amarelo (proteção)</t>
+  </si>
+  <si>
+    <t>4, 5, 6, 9</t>
+  </si>
+  <si>
+    <t>Condutor isolado 450/750 V, cobre classe 5, PVC 70 °C — 10 mm², cor vermelho (fase)</t>
+  </si>
+  <si>
+    <t>Condutor isolado 450/750 V, cobre classe 5, PVC 70 °C — 10 mm², cor branco (fase)</t>
+  </si>
+  <si>
+    <t>Condutor isolado 450/750 V, cobre classe 5, PVC 70 °C — 10 mm², cor verde-amarelo (proteção)</t>
+  </si>
+  <si>
+    <t>Cabo unipolar 0,6/1 kV, cobre classe 5, PVC 70 °C — 2,5 mm², cor preto (fase)</t>
+  </si>
+  <si>
+    <t>ABNT NBR 7288</t>
+  </si>
+  <si>
+    <t>Cabo unipolar 0,6/1 kV, cobre classe 5, PVC 70 °C — 2,5 mm², cor branco (fase)</t>
+  </si>
+  <si>
+    <t>Cabo unipolar 0,6/1 kV, cobre classe 5, PVC 70 °C — 2,5 mm², cor verde-amarelo (proteção)</t>
+  </si>
+  <si>
+    <t>Cabo unipolar 0,6/1 kV, cobre classe 5, PVC 70 °C — 16 mm², cor preto (fase)</t>
+  </si>
+  <si>
+    <t>Cabo unipolar 0,6/1 kV, cobre classe 5, PVC 70 °C — 16 mm², cor vermelho (fase)</t>
+  </si>
+  <si>
+    <t>Cabo unipolar 0,6/1 kV, cobre classe 5, PVC 70 °C — 16 mm², cor branco (fase)</t>
+  </si>
+  <si>
+    <t>Cabo unipolar 0,6/1 kV, cobre classe 5, PVC 70 °C — 16 mm², cor azul-claro (neutro)</t>
+  </si>
+  <si>
+    <t>Cabo unipolar 0,6/1 kV, cobre classe 5, PVC 70 °C — 16 mm², cor verde-amarelo (proteção)</t>
+  </si>
+  <si>
+    <t>Dispositivos de proteção</t>
+  </si>
+  <si>
+    <t>Disjuntor termomagnético 1P curva C 10 A — 6,0 kA</t>
+  </si>
+  <si>
+    <t>ABNT NBR NM 60898</t>
+  </si>
+  <si>
+    <t>1, 2, 11, 12</t>
+  </si>
+  <si>
+    <t>Disjuntor termomagnético 1P curva C 16 A — 6,0 kA</t>
+  </si>
+  <si>
+    <t>3, 4, 5, 9</t>
+  </si>
+  <si>
+    <t>Disjuntor termomagnético 2P curva C 10 A — 6,0 kA</t>
+  </si>
+  <si>
+    <t>8, 10</t>
+  </si>
+  <si>
+    <t>Disjuntor termomagnético 2P curva C 25 A — 6,0 kA</t>
+  </si>
+  <si>
+    <t>Disjuntor termomagnético 2P curva C 40 A — 6,0 kA</t>
+  </si>
+  <si>
+    <t>Disjuntor termomagnético 3P curva C 63 A — 6,0 kA</t>
+  </si>
+  <si>
+    <t>Interruptor diferencial-residual (IDR) 2P 25 A — 30 mA</t>
+  </si>
+  <si>
+    <t>ABNT NBR NM 61008</t>
+  </si>
+  <si>
+    <t>2, 4, 5, 6, 9, 10, 11, 12</t>
+  </si>
+  <si>
+    <t>Interruptor diferencial-residual (IDR) 2P 40 A — 30 mA</t>
+  </si>
+  <si>
+    <t>DPS classe II — 275 V, In 20 kA, Imáx 40 kA</t>
+  </si>
+  <si>
+    <t>ABNT NBR IEC 61643-11</t>
+  </si>
+  <si>
+    <t>cadastro</t>
+  </si>
+  <si>
+    <t>Quadros de distribuição</t>
+  </si>
+  <si>
+    <t>Quadro de distribuição QD-1 (Quadro de distribuição de circuitos) — 40 módulos DIN, com barramentos de fase, neutro e proteção; 12 circuitos + reserva para 3 circuitos (Tabela 59)</t>
+  </si>
+  <si>
+    <t>ABNT NBR IEC 61439-3</t>
+  </si>
+  <si>
+    <t>Barramento de neutro com bornes</t>
+  </si>
+  <si>
+    <t>Barramento de proteção (terra) com bornes</t>
+  </si>
+  <si>
+    <t>Eletrodutos, eletrocalhas e acessórios</t>
+  </si>
+  <si>
+    <t>Eletroduto PVC rígido roscável DN 25 (3/4")</t>
+  </si>
+  <si>
+    <t>ABNT NBR 15465</t>
+  </si>
+  <si>
+    <t>E1, E3, circ. 10</t>
+  </si>
+  <si>
+    <t>Eletroduto PVC rígido roscável DN 32 (1")</t>
+  </si>
+  <si>
+    <t>E2</t>
+  </si>
+  <si>
+    <t>Eletroduto PVC rígido roscável DN 40 (1 1/4")</t>
+  </si>
+  <si>
+    <t>circ. AL-1</t>
+  </si>
+  <si>
+    <t>Perfilado com tampa 38 × 38 mm, com tampa, emendas e acessórios</t>
+  </si>
+  <si>
+    <t>ABNT NBR IEC 61537</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>Suporte / suspensão para perfilado com tampa 38 mm</t>
+  </si>
+  <si>
+    <t>Caixas</t>
+  </si>
+  <si>
+    <t>Caixa de embutir 4×2" em PVC</t>
+  </si>
+  <si>
+    <t>ABNT NBR IEC 60670-1</t>
+  </si>
+  <si>
+    <t>Caixa octogonal 4×4" com fundo móvel (laje)</t>
+  </si>
+  <si>
+    <t>Tomadas, interruptores e dispositivos de comando</t>
+  </si>
+  <si>
+    <t>Tomada 2P+T 10 A — 250 V com placa 4×2"</t>
+  </si>
+  <si>
+    <t>ABNT NBR 14136; NBR NM 60884-1</t>
+  </si>
+  <si>
+    <t>Tomada 2P+T 20 A — 250 V com placa 4×2"</t>
+  </si>
+  <si>
+    <t>Interruptor simples 10 A com placa 4×2"</t>
+  </si>
+  <si>
+    <t>ABNT NBR NM 60669-1</t>
+  </si>
+  <si>
+    <t>Interruptor paralelo (three-way) 10 A com placa 4×2"</t>
+  </si>
+  <si>
+    <t>Saída de fio com placa 4×2" (ponto de força, chuveiro)</t>
+  </si>
+  <si>
+    <t>Luminária Ledvance Plafon LED slim quadrado 18 W 4000 K</t>
+  </si>
+  <si>
+    <t>ABNT NBR IEC 60598-1</t>
+  </si>
+  <si>
+    <t>Luminária Philips Plafon LED de sobrepor redondo 18 W 4000 K</t>
+  </si>
+  <si>
+    <t>Luminária Ledvance Downlight LED de embutir 12 W</t>
+  </si>
+  <si>
+    <t>Luminária Lumicenter EF40-E — downlight 17,5 W (EF40-E12000840)</t>
+  </si>
+  <si>
+    <t>Aterramento e equipotencialização</t>
+  </si>
+  <si>
+    <t>Haste de aterramento aço-cobreada (NBR 13571) — 3/4" × 2,40 m</t>
+  </si>
+  <si>
+    <t>ABNT NBR 13571</t>
+  </si>
+  <si>
+    <t>Padrão de entrada — categoria T3 (NDU 001)</t>
+  </si>
+  <si>
+    <t>Conector cabo–haste (cunha, grampo ou solda exotérmica)</t>
+  </si>
+  <si>
+    <t>ABNT NBR 16254</t>
+  </si>
+  <si>
+    <t>Caixa de inspeção de aterramento com tampa</t>
+  </si>
+  <si>
+    <t>Cabo de cobre nu 16 mm² — interligação das hastes (enterrado a 0,50 m)</t>
+  </si>
+  <si>
+    <t>Condutor de aterramento 16 mm² — da primeira haste ao quadro / BEP</t>
+  </si>
+  <si>
+    <t>Eletroduto de proteção do condutor de aterramento</t>
+  </si>
+  <si>
+    <t>Barramento de equipotencialização principal (BEP) em cobre</t>
+  </si>
+  <si>
+    <t>ABNT NBR 5410 (6.4.2)</t>
+  </si>
+  <si>
+    <t>Materiais diversos</t>
+  </si>
+  <si>
+    <t>Conector de emenda/derivação por alavanca (2 a 5 vias)</t>
+  </si>
+  <si>
+    <t>Fita isolante de PVC 19 mm × 20 m</t>
+  </si>
+  <si>
+    <t>rolo</t>
+  </si>
+  <si>
+    <t>Anilhas/etiquetas de identificação de circuitos</t>
+  </si>
+  <si>
+    <t>cj</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="#,##0.##"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -1008,7 +1382,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1062,6 +1436,9 @@
     <xf numFmtId="2" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2367,6 +2744,1839 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H72"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="62" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="7" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G6" s="29">
+        <v>1</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>2</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G7" s="29">
+        <v>1</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="G8" s="29">
+        <v>1</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="G9" s="29">
+        <v>1</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G10" s="29">
+        <v>49</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>6</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G11" s="29">
+        <v>20</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>7</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G12" s="29">
+        <v>69</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>8</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G13" s="29">
+        <v>69</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>9</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G14" s="29">
+        <v>21</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
+        <v>10</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G15" s="29">
+        <v>25</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>11</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G16" s="29">
+        <v>46</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>12</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G17" s="29">
+        <v>49</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
+        <v>13</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G18" s="29">
+        <v>70</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
+        <v>14</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G19" s="29">
+        <v>32</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="5">
+        <v>15</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G20" s="29">
+        <v>36</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
+        <v>16</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G21" s="29">
+        <v>14</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
+        <v>17</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G22" s="29">
+        <v>48</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
+        <v>18</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G23" s="29">
+        <v>64</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="5">
+        <v>19</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G24" s="29">
+        <v>24</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
+        <v>20</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G25" s="29">
+        <v>24</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="5">
+        <v>21</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G26" s="29">
+        <v>24</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="5">
+        <v>22</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G27" s="29">
+        <v>31</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="5">
+        <v>23</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G28" s="29">
+        <v>31</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
+        <v>24</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G29" s="29">
+        <v>31</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="5">
+        <v>25</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G30" s="29">
+        <v>14</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
+        <v>26</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G31" s="29">
+        <v>14</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="5">
+        <v>27</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G32" s="29">
+        <v>14</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
+        <v>28</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G33" s="29">
+        <v>14</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
+        <v>29</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G34" s="29">
+        <v>14</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
+        <v>30</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G35" s="29">
+        <v>4</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="5">
+        <v>31</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G36" s="29">
+        <v>4</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="5">
+        <v>32</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G37" s="29">
+        <v>2</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="5">
+        <v>33</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G38" s="29">
+        <v>1</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="5">
+        <v>34</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G39" s="29">
+        <v>1</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="5">
+        <v>35</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G40" s="29">
+        <v>1</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="5">
+        <v>36</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G41" s="29">
+        <v>8</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="5">
+        <v>37</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G42" s="29">
+        <v>1</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="5">
+        <v>38</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G43" s="29">
+        <v>4</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="5">
+        <v>39</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G44" s="29">
+        <v>1</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="5">
+        <v>40</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G45" s="29">
+        <v>1</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="5">
+        <v>41</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G46" s="29">
+        <v>1</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="5">
+        <v>42</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G47" s="29">
+        <v>51</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="5">
+        <v>43</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G48" s="29">
+        <v>9</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="5">
+        <v>44</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G49" s="29">
+        <v>14</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="5">
+        <v>45</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G50" s="29">
+        <v>14</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="5">
+        <v>46</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G51" s="29">
+        <v>9</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="5">
+        <v>47</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G52" s="29">
+        <v>30</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="5">
+        <v>48</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G53" s="29">
+        <v>14</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="5">
+        <v>49</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G54" s="29">
+        <v>18</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="5">
+        <v>50</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G55" s="29">
+        <v>4</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="5">
+        <v>51</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G56" s="29">
+        <v>8</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="5">
+        <v>52</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G57" s="29">
+        <v>2</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="5">
+        <v>53</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G58" s="29">
+        <v>3</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="5">
+        <v>54</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G59" s="29">
+        <v>4</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="5">
+        <v>55</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G60" s="29">
+        <v>4</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="5">
+        <v>56</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G61" s="29">
+        <v>8</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="5">
+        <v>57</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G62" s="29">
+        <v>6</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="5">
+        <v>58</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G63" s="29">
+        <v>4</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="5">
+        <v>59</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G64" s="29">
+        <v>4</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="5">
+        <v>60</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G65" s="29">
+        <v>4</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="5">
+        <v>61</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G66" s="29">
+        <v>8</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="5">
+        <v>62</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G67" s="29">
+        <v>3</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="5">
+        <v>63</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G68" s="29">
+        <v>3</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="5">
+        <v>64</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G69" s="29">
+        <v>1</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="5">
+        <v>65</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G70" s="29">
+        <v>40</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="5">
+        <v>66</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="G71" s="29">
+        <v>5</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="5">
+        <v>67</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="G72" s="29">
+        <v>1</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>370</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:H72"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>

--- a/exemplo/quadro-de-cargas-residencia-unifamiliar-exemplo-r00.xlsx
+++ b/exemplo/quadro-de-cargas-residencia-unifamiliar-exemplo-r00.xlsx
@@ -10,18 +10,19 @@
     <sheet sheetId="4" name="Eletrodutos" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="Eletrocalhas" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="Luminotécnico" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Demanda Energisa" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Cargas Energisa" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Carga térmica" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Perfil horário" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="Lista de materiais" state="visible" r:id="rId14"/>
+    <sheet sheetId="7" name="Iluminação externa" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Demanda Energisa" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Cargas Energisa" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Carga térmica" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Perfil horário" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="Lista de materiais" state="visible" r:id="rId15"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="457">
   <si>
     <t>Quadro de cargas — QM — Quadro de medição (ponto de entrega)</t>
   </si>
@@ -29,7 +30,7 @@
     <t>Obra: Residência unifamiliar — exemplo — Proprietário (exemplo)</t>
   </si>
   <si>
-    <t>Sistema: 127/220 V, trifásico, esquema TN-S · Responsável: Nome do responsável técnico — CREA/CFT nº 000000 · R00 · 20/10/2026</t>
+    <t>Sistema: 127/220 V, trifásico, esquema TN-S · Responsável: Nome do responsável técnico — CREA/CFT nº 000000 · R00 · 26/10/2026</t>
   </si>
   <si>
     <t>Circ.</t>
@@ -293,6 +294,12 @@
     <t>TUG — garagem (perfilado)</t>
   </si>
   <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Iluminação externa — estacionamento</t>
+  </si>
+  <si>
     <t>Alimentado pelo circuito AL-1 (quadro QM)</t>
   </si>
   <si>
@@ -383,6 +390,9 @@
     <t>Perfilado com tampa 38×38 mm</t>
   </si>
   <si>
+    <t>PVC rígido roscável DN 20 (1/2")</t>
+  </si>
+  <si>
     <t>QM</t>
   </si>
   <si>
@@ -452,6 +462,9 @@
     <t>Exclusivo — circuito 10</t>
   </si>
   <si>
+    <t>Exclusivo — circuito 13</t>
+  </si>
+  <si>
     <t>Exclusivo — circuito AL-1</t>
   </si>
   <si>
@@ -620,6 +633,63 @@
     <t>Confirmar na ficha fotométrica do fabricante que o UGR da instalação não ultrapassa UGRL = 19.</t>
   </si>
   <si>
+    <t>Iluminação de exteriores — método dos lúmens e ponto a ponto (NBR 5101 / EN 12464-2)</t>
+  </si>
+  <si>
+    <t>Área</t>
+  </si>
+  <si>
+    <t>Requisito</t>
+  </si>
+  <si>
+    <t>W (m)</t>
+  </si>
+  <si>
+    <t>Eméd exig. (lx)</t>
+  </si>
+  <si>
+    <t>U0 exig.</t>
+  </si>
+  <si>
+    <t>Projetor</t>
+  </si>
+  <si>
+    <t>Facho (°)</t>
+  </si>
+  <si>
+    <t>Postes</t>
+  </si>
+  <si>
+    <t>h (m)</t>
+  </si>
+  <si>
+    <t>Incl. (°)</t>
+  </si>
+  <si>
+    <t>Fu</t>
+  </si>
+  <si>
+    <t>Fd</t>
+  </si>
+  <si>
+    <t>Eméd pp (lx)</t>
+  </si>
+  <si>
+    <t>U0</t>
+  </si>
+  <si>
+    <t>Estacionamento externo</t>
+  </si>
+  <si>
+    <t>Estacionamento de tráfego médio (escritórios, shoppings)</t>
+  </si>
+  <si>
+    <t>Refletor LED 50 W</t>
+  </si>
+  <si>
+    <t>Postes nos dois lados (frente a frente)</t>
+  </si>
+  <si>
     <t>Demanda — Energisa Mato Grosso do Sul · Unidade consumidora individual (NDU 001) · 220/127 V — rede trifásica (Tabela 16)</t>
   </si>
   <si>
@@ -1055,12 +1125,21 @@
     <t>Condutor isolado 450/750 V, cobre classe 5, PVC 70 °C — 10 mm², cor verde-amarelo (proteção)</t>
   </si>
   <si>
+    <t>Cabo unipolar 0,6/1 kV, cobre classe 5, PVC 70 °C — 1,5 mm², cor branco (fase)</t>
+  </si>
+  <si>
+    <t>ABNT NBR 7288</t>
+  </si>
+  <si>
+    <t>Cabo unipolar 0,6/1 kV, cobre classe 5, PVC 70 °C — 1,5 mm², cor azul-claro (neutro)</t>
+  </si>
+  <si>
+    <t>Cabo unipolar 0,6/1 kV, cobre classe 5, PVC 70 °C — 1,5 mm², cor verde-amarelo (proteção)</t>
+  </si>
+  <si>
     <t>Cabo unipolar 0,6/1 kV, cobre classe 5, PVC 70 °C — 2,5 mm², cor preto (fase)</t>
   </si>
   <si>
-    <t>ABNT NBR 7288</t>
-  </si>
-  <si>
     <t>Cabo unipolar 0,6/1 kV, cobre classe 5, PVC 70 °C — 2,5 mm², cor branco (fase)</t>
   </si>
   <si>
@@ -1091,7 +1170,7 @@
     <t>ABNT NBR NM 60898</t>
   </si>
   <si>
-    <t>1, 2, 11, 12</t>
+    <t>1, 2, 11, 12, 13</t>
   </si>
   <si>
     <t>Disjuntor termomagnético 1P curva C 16 A — 6,0 kA</t>
@@ -1121,7 +1200,7 @@
     <t>ABNT NBR NM 61008</t>
   </si>
   <si>
-    <t>2, 4, 5, 6, 9, 10, 11, 12</t>
+    <t>2, 4, 5, 6, 9, 10, 11, 12, 13</t>
   </si>
   <si>
     <t>Interruptor diferencial-residual (IDR) 2P 40 A — 30 mA</t>
@@ -1139,7 +1218,7 @@
     <t>Quadros de distribuição</t>
   </si>
   <si>
-    <t>Quadro de distribuição QD-1 (Quadro de distribuição de circuitos) — 40 módulos DIN, com barramentos de fase, neutro e proteção; 12 circuitos + reserva para 3 circuitos (Tabela 59)</t>
+    <t>Quadro de distribuição QD-1 (Quadro de distribuição de circuitos) — 48 módulos DIN, com barramentos de fase, neutro e proteção; 13 circuitos + reserva para 4 circuitos (Tabela 59)</t>
   </si>
   <si>
     <t>ABNT NBR IEC 61439-3</t>
@@ -1169,6 +1248,12 @@
     <t>E2</t>
   </si>
   <si>
+    <t>Eletroduto PVC rígido roscável DN 20 (1/2")</t>
+  </si>
+  <si>
+    <t>circ. 13</t>
+  </si>
+  <si>
     <t>Eletroduto PVC rígido roscável DN 40 (1 1/4")</t>
   </si>
   <si>
@@ -1236,6 +1321,24 @@
   </si>
   <si>
     <t>Luminária Lumicenter EF40-E — downlight 17,5 W (EF40-E12000840)</t>
+  </si>
+  <si>
+    <t>Refletor LED 50 W — 5.000 lm, facho 120°, IP65 mín., com braço/suporte</t>
+  </si>
+  <si>
+    <t>ABNT NBR IEC 60598-1 / IEC 60598-2-5</t>
+  </si>
+  <si>
+    <t>Poste de aço galvanizado a fogo, altura útil 7,0 m, com base, chumbadores e caixa de passagem</t>
+  </si>
+  <si>
+    <t>ABNT NBR 14744</t>
+  </si>
+  <si>
+    <t>Relé fotoelétrico (ou temporizador) para comando da iluminação externa</t>
+  </si>
+  <si>
+    <t>ABNT NBR 5123</t>
   </si>
   <si>
     <t>Aterramento e equipotencialização</t>
@@ -1946,16 +2049,16 @@
         <v>26</v>
       </c>
       <c r="F6" s="7">
-        <v>22195.76</v>
+        <v>22395.76</v>
       </c>
       <c r="G6" s="8">
         <v>0.94</v>
       </c>
       <c r="H6" s="7">
-        <v>23621.14</v>
+        <v>23831.67</v>
       </c>
       <c r="I6" s="8">
-        <v>61.99</v>
+        <v>62.54</v>
       </c>
       <c r="J6" s="8">
         <v>1</v>
@@ -1973,16 +2076,16 @@
         <v>29</v>
       </c>
       <c r="O6" s="8">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="P6" s="7">
-        <v>7873.71</v>
+        <v>7943.89</v>
       </c>
       <c r="Q6" s="7">
-        <v>7873.71</v>
+        <v>7943.89</v>
       </c>
       <c r="R6" s="7">
-        <v>7873.71</v>
+        <v>7943.89</v>
       </c>
       <c r="S6" s="5" t="s">
         <v>30</v>
@@ -1998,12 +2101,12 @@
       <c r="E7" s="9"/>
       <c r="F7" s="10">
         <f>SUM(F6:F6)</f>
-        <v>22195.76</v>
+        <v>22395.76</v>
       </c>
       <c r="G7" s="9"/>
       <c r="H7" s="10">
         <f>SUM(H6:H6)</f>
-        <v>23621.14</v>
+        <v>23831.67</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
@@ -2014,15 +2117,15 @@
       <c r="O7" s="9"/>
       <c r="P7" s="10">
         <f>SUM(P6:P6)</f>
-        <v>7873.71</v>
+        <v>7943.89</v>
       </c>
       <c r="Q7" s="10">
         <f>SUM(Q6:Q6)</f>
-        <v>7873.71</v>
+        <v>7943.89</v>
       </c>
       <c r="R7" s="10">
         <f>SUM(R6:R6)</f>
-        <v>7873.71</v>
+        <v>7943.89</v>
       </c>
       <c r="S7" s="9"/>
     </row>
@@ -2053,7 +2156,7 @@
       <c r="D11" s="12"/>
       <c r="E11" s="13">
         <f>SUMIF(C6:C6,"Distribuição (alimentador de quadro)",H6:H6)</f>
-        <v>23621.14</v>
+        <v>23831.67</v>
       </c>
       <c r="F11" s="13"/>
     </row>
@@ -2088,7 +2191,7 @@
       <c r="D14" s="12"/>
       <c r="E14" s="13">
         <f>IF(N(E13)&gt;0,E13*1000,E12*E10+E11)</f>
-        <v>23621.14</v>
+        <v>23831.67</v>
       </c>
       <c r="F14" s="13"/>
     </row>
@@ -2101,7 +2204,7 @@
       <c r="D15" s="12"/>
       <c r="E15" s="17">
         <f>E14/(SQRT(3)*220)</f>
-        <v>61.99</v>
+        <v>62.54</v>
       </c>
       <c r="F15" s="17"/>
     </row>
@@ -2170,6 +2273,341 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P9"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="4" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="7" customWidth="1"/>
+    <col min="8" max="10" width="8" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="7" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="22" customWidth="1"/>
+    <col min="15" max="15" width="11" customWidth="1"/>
+    <col min="16" max="16" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="B6" s="8">
+        <v>10.2</v>
+      </c>
+      <c r="C6" s="21">
+        <v>2</v>
+      </c>
+      <c r="D6" s="7">
+        <v>2303</v>
+      </c>
+      <c r="E6" s="7">
+        <v>63</v>
+      </c>
+      <c r="F6" s="7">
+        <f>D6+E6</f>
+        <v>2366</v>
+      </c>
+      <c r="G6" s="8">
+        <v>0.97</v>
+      </c>
+      <c r="H6" s="21">
+        <v>17</v>
+      </c>
+      <c r="I6" s="21">
+        <v>232</v>
+      </c>
+      <c r="J6" s="24">
+        <v>0.1</v>
+      </c>
+      <c r="K6" s="7">
+        <f>F6*(1+J6)*3.412142</f>
+        <v>8879</v>
+      </c>
+      <c r="L6" s="8">
+        <f>F6*(1+J6)/3516.85</f>
+        <v>0.74</v>
+      </c>
+      <c r="M6" s="22">
+        <v>0</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="O6" s="7">
+        <v>824</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B7" s="8">
+        <v>16.2</v>
+      </c>
+      <c r="C7" s="21">
+        <v>4</v>
+      </c>
+      <c r="D7" s="7">
+        <v>2456</v>
+      </c>
+      <c r="E7" s="7">
+        <v>280</v>
+      </c>
+      <c r="F7" s="7">
+        <f>D7+E7</f>
+        <v>2736</v>
+      </c>
+      <c r="G7" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="H7" s="21">
+        <v>15</v>
+      </c>
+      <c r="I7" s="21">
+        <v>169</v>
+      </c>
+      <c r="J7" s="24">
+        <v>0.1</v>
+      </c>
+      <c r="K7" s="7">
+        <f>F7*(1+J7)*3.412142</f>
+        <v>10270</v>
+      </c>
+      <c r="L7" s="8">
+        <f>F7*(1+J7)/3516.85</f>
+        <v>0.86</v>
+      </c>
+      <c r="M7" s="22">
+        <v>0</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="O7" s="7">
+        <v>1099</v>
+      </c>
+      <c r="P7" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="B8" s="8">
+        <v>8.32</v>
+      </c>
+      <c r="C8" s="21">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7">
+        <v>2096</v>
+      </c>
+      <c r="E8" s="7">
+        <v>137</v>
+      </c>
+      <c r="F8" s="7">
+        <f>D8+E8</f>
+        <v>2234</v>
+      </c>
+      <c r="G8" s="8">
+        <v>0.94</v>
+      </c>
+      <c r="H8" s="21">
+        <v>16</v>
+      </c>
+      <c r="I8" s="21">
+        <v>268</v>
+      </c>
+      <c r="J8" s="24">
+        <v>0.1</v>
+      </c>
+      <c r="K8" s="7">
+        <f>F8*(1+J8)*3.412142</f>
+        <v>8383</v>
+      </c>
+      <c r="L8" s="8">
+        <f>F8*(1+J8)/3516.85</f>
+        <v>0.7</v>
+      </c>
+      <c r="M8" s="22">
+        <v>5</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="O8" s="7">
+        <v>824</v>
+      </c>
+      <c r="P8" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="B9" s="26">
+        <f>SUM(B6:B8)</f>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="10">
+        <f>SUM(D6:D8)</f>
+      </c>
+      <c r="E9" s="10">
+        <f>SUM(E6:E8)</f>
+      </c>
+      <c r="F9" s="10">
+        <f>SUM(F6:F8)</f>
+      </c>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="10">
+        <f>SUM(K6:K8)</f>
+      </c>
+      <c r="L9" s="26">
+        <f>SUM(L6:L8)</f>
+      </c>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="10">
+        <f>SUM(O6:O8)</f>
+      </c>
+      <c r="P9" s="9"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:P8"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A3:P3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -2180,7 +2618,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2210,22 +2648,22 @@
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>298</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -2744,12 +3182,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2763,7 +3201,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>299</v>
+        <v>322</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2799,28 +3237,28 @@
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>305</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -2828,25 +3266,25 @@
         <v>1</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>306</v>
+        <v>329</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="G6" s="29">
         <v>1</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -2854,25 +3292,25 @@
         <v>2</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>306</v>
+        <v>329</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>311</v>
+        <v>334</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="G7" s="29">
         <v>1</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -2880,25 +3318,25 @@
         <v>3</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>306</v>
+        <v>329</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="G8" s="29">
         <v>1</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -2906,25 +3344,25 @@
         <v>4</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>306</v>
+        <v>329</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="G9" s="29">
         <v>1</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -2932,25 +3370,25 @@
         <v>5</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>316</v>
+        <v>339</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="G10" s="29">
         <v>49</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>319</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -2958,19 +3396,19 @@
         <v>6</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>320</v>
+        <v>343</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="G11" s="29">
         <v>20</v>
@@ -2984,25 +3422,25 @@
         <v>7</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="G12" s="29">
         <v>69</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>322</v>
+        <v>345</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -3010,25 +3448,25 @@
         <v>8</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>323</v>
+        <v>346</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="G13" s="29">
         <v>69</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>322</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -3036,19 +3474,19 @@
         <v>9</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>324</v>
+        <v>347</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="G14" s="29">
         <v>21</v>
@@ -3062,19 +3500,19 @@
         <v>10</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="G15" s="29">
         <v>25</v>
@@ -3088,25 +3526,25 @@
         <v>11</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="G16" s="29">
         <v>46</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>327</v>
+        <v>350</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -3114,25 +3552,25 @@
         <v>12</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>328</v>
+        <v>351</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="G17" s="29">
         <v>49</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>329</v>
+        <v>352</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -3140,25 +3578,25 @@
         <v>13</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>330</v>
+        <v>353</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="G18" s="29">
         <v>70</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>331</v>
+        <v>354</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -3166,25 +3604,25 @@
         <v>14</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>332</v>
+        <v>355</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="G19" s="29">
         <v>32</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>333</v>
+        <v>356</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -3192,25 +3630,25 @@
         <v>15</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>334</v>
+        <v>357</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="G20" s="29">
         <v>36</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>335</v>
+        <v>358</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -3218,19 +3656,19 @@
         <v>16</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>336</v>
+        <v>359</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="G21" s="29">
         <v>14</v>
@@ -3244,25 +3682,25 @@
         <v>17</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="G22" s="29">
         <v>48</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>338</v>
+        <v>361</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -3270,25 +3708,25 @@
         <v>18</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="G23" s="29">
         <v>64</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>340</v>
+        <v>363</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -3296,19 +3734,19 @@
         <v>19</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C24" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F24" s="5" t="s">
         <v>341</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>318</v>
       </c>
       <c r="G24" s="29">
         <v>24</v>
@@ -3322,19 +3760,19 @@
         <v>20</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="G25" s="29">
         <v>24</v>
@@ -3348,19 +3786,19 @@
         <v>21</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="G26" s="29">
         <v>24</v>
@@ -3374,25 +3812,25 @@
         <v>22</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>344</v>
+        <v>367</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="G27" s="29">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -3400,25 +3838,25 @@
         <v>23</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="G28" s="29">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -3426,25 +3864,25 @@
         <v>24</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>347</v>
+        <v>370</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="G29" s="29">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -3452,25 +3890,25 @@
         <v>25</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="G30" s="29">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -3478,25 +3916,25 @@
         <v>26</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="G31" s="29">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -3504,25 +3942,25 @@
         <v>27</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="G32" s="29">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -3530,19 +3968,19 @@
         <v>28</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="G33" s="29">
         <v>14</v>
@@ -3556,19 +3994,19 @@
         <v>29</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>352</v>
+        <v>375</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="G34" s="29">
         <v>14</v>
@@ -3582,25 +4020,25 @@
         <v>30</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>309</v>
+        <v>341</v>
       </c>
       <c r="G35" s="29">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>356</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -3608,25 +4046,25 @@
         <v>31</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>309</v>
+        <v>341</v>
       </c>
       <c r="G36" s="29">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>358</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -3634,25 +4072,25 @@
         <v>32</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>309</v>
+        <v>341</v>
       </c>
       <c r="G37" s="29">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>360</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -3660,25 +4098,25 @@
         <v>33</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="G38" s="29">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>64</v>
+        <v>382</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -3686,25 +4124,25 @@
         <v>34</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="G39" s="29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>71</v>
+        <v>384</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -3712,25 +4150,25 @@
         <v>35</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>363</v>
+        <v>385</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="G40" s="29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>22</v>
+        <v>386</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -3738,25 +4176,25 @@
         <v>36</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>365</v>
+        <v>381</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="G41" s="29">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>366</v>
+        <v>64</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -3764,19 +4202,19 @@
         <v>37</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>365</v>
+        <v>381</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="G42" s="29">
         <v>1</v>
@@ -3790,25 +4228,25 @@
         <v>38</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="G43" s="29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>370</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -3816,25 +4254,25 @@
         <v>39</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="G44" s="29">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>103</v>
+        <v>392</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -3842,25 +4280,25 @@
         <v>40</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="G45" s="29">
         <v>1</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>370</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -3868,25 +4306,25 @@
         <v>41</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>373</v>
+        <v>395</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="G46" s="29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>370</v>
+        <v>396</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -3894,25 +4332,25 @@
         <v>42</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="G47" s="29">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>379</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -3920,25 +4358,25 @@
         <v>43</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="G48" s="29">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>381</v>
+        <v>396</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -3946,25 +4384,25 @@
         <v>44</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="G49" s="29">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -3972,25 +4410,25 @@
         <v>45</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>376</v>
+        <v>402</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="G50" s="29">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>386</v>
+        <v>405</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -3998,25 +4436,25 @@
         <v>46</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>376</v>
+        <v>402</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>309</v>
+        <v>341</v>
       </c>
       <c r="G51" s="29">
         <v>9</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -4024,25 +4462,25 @@
         <v>47</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>309</v>
+        <v>341</v>
       </c>
       <c r="G52" s="29">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>370</v>
+        <v>409</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -4050,25 +4488,25 @@
         <v>48</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>309</v>
+        <v>341</v>
       </c>
       <c r="G53" s="29">
         <v>14</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>370</v>
+        <v>411</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -4076,25 +4514,25 @@
         <v>49</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>309</v>
+        <v>341</v>
       </c>
       <c r="G54" s="29">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>370</v>
+        <v>414</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -4102,25 +4540,25 @@
         <v>50</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="G55" s="29">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>370</v>
+        <v>414</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -4128,25 +4566,25 @@
         <v>51</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>392</v>
+        <v>416</v>
       </c>
       <c r="C56" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="G56" s="29">
+        <v>30</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>396</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>397</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="F56" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="G56" s="29">
-        <v>8</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -4154,25 +4592,25 @@
         <v>52</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>392</v>
+        <v>416</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>398</v>
+        <v>419</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="G57" s="29">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>370</v>
+        <v>396</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -4180,25 +4618,25 @@
         <v>53</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>392</v>
+        <v>420</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>399</v>
+        <v>421</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>390</v>
+        <v>422</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="G58" s="29">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>370</v>
+        <v>396</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -4206,25 +4644,25 @@
         <v>54</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>44</v>
+        <v>420</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>400</v>
+        <v>423</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="G59" s="29">
         <v>4</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>182</v>
+        <v>396</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -4232,25 +4670,25 @@
         <v>55</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>44</v>
+        <v>420</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="G60" s="29">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>186</v>
+        <v>396</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -4258,25 +4696,25 @@
         <v>56</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>44</v>
+        <v>420</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="G61" s="29">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>189</v>
+        <v>396</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -4284,25 +4722,25 @@
         <v>57</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>44</v>
+        <v>420</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>404</v>
+        <v>427</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>401</v>
+        <v>418</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="G62" s="29">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>193</v>
+        <v>396</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -4310,25 +4748,25 @@
         <v>58</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>405</v>
+        <v>44</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="G63" s="29">
         <v>4</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>408</v>
+        <v>186</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -4336,25 +4774,25 @@
         <v>59</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>405</v>
+        <v>44</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>410</v>
+        <v>429</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="G64" s="29">
         <v>4</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>408</v>
+        <v>190</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -4362,25 +4800,25 @@
         <v>60</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>405</v>
+        <v>44</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>411</v>
+        <v>431</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>108</v>
+        <v>429</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="G65" s="29">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>408</v>
+        <v>193</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -4388,25 +4826,25 @@
         <v>61</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>405</v>
+        <v>44</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>410</v>
+        <v>429</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="G66" s="29">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>408</v>
+        <v>197</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -4414,25 +4852,25 @@
         <v>62</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>405</v>
+        <v>44</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>410</v>
+        <v>434</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="G67" s="29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>408</v>
+        <v>218</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -4440,25 +4878,25 @@
         <v>63</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>405</v>
+        <v>44</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>378</v>
+        <v>436</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="G68" s="29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>408</v>
+        <v>218</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -4466,25 +4904,25 @@
         <v>64</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>405</v>
+        <v>44</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>415</v>
+        <v>437</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>416</v>
+        <v>438</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="G69" s="29">
         <v>1</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>370</v>
+        <v>218</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -4492,25 +4930,25 @@
         <v>65</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>417</v>
+        <v>439</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>108</v>
+        <v>441</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="G70" s="29">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>370</v>
+        <v>442</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -4518,25 +4956,25 @@
         <v>66</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>417</v>
+        <v>439</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>419</v>
+        <v>443</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>108</v>
+        <v>444</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>420</v>
+        <v>332</v>
       </c>
       <c r="G71" s="29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>370</v>
+        <v>442</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -4544,29 +4982,211 @@
         <v>67</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>417</v>
+        <v>439</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>421</v>
+        <v>445</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>422</v>
+        <v>332</v>
       </c>
       <c r="G72" s="29">
+        <v>4</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="5">
+        <v>68</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="G73" s="29">
+        <v>8</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="5">
+        <v>69</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="G74" s="29">
+        <v>3</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="5">
+        <v>70</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="G75" s="29">
+        <v>3</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="5">
+        <v>71</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="G76" s="29">
         <v>1</v>
       </c>
-      <c r="H72" s="6" t="s">
-        <v>370</v>
+      <c r="H76" s="6" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="5">
+        <v>72</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="G77" s="29">
+        <v>40</v>
+      </c>
+      <c r="H77" s="6" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="5">
+        <v>73</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="G78" s="29">
+        <v>5</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="5">
+        <v>74</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="G79" s="29">
+        <v>1</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>396</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:H72"/>
+  <autoFilter ref="A5:H79"/>
   <mergeCells count="3">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
@@ -4582,7 +5202,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S30"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -4774,7 +5394,7 @@
         <v>29</v>
       </c>
       <c r="O6" s="8">
-        <v>4.23</v>
+        <v>4.24</v>
       </c>
       <c r="P6" s="7">
         <v>780</v>
@@ -4829,7 +5449,7 @@
         <v>52</v>
       </c>
       <c r="O7" s="8">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="P7" s="7"/>
       <c r="Q7" s="7">
@@ -4994,7 +5614,7 @@
         <v>52</v>
       </c>
       <c r="O10" s="8">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="P10" s="7"/>
       <c r="Q10" s="7">
@@ -5049,7 +5669,7 @@
         <v>52</v>
       </c>
       <c r="O11" s="8">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="P11" s="7">
         <v>2750</v>
@@ -5106,7 +5726,7 @@
         <v>76</v>
       </c>
       <c r="O12" s="8">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="P12" s="7"/>
       <c r="Q12" s="7">
@@ -5163,7 +5783,7 @@
         <v>29</v>
       </c>
       <c r="O13" s="8">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="P13" s="7">
         <v>722.22</v>
@@ -5220,7 +5840,7 @@
         <v>52</v>
       </c>
       <c r="O14" s="8">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
@@ -5332,7 +5952,7 @@
         <v>52</v>
       </c>
       <c r="O16" s="8">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="P16" s="7">
         <v>300</v>
@@ -5387,7 +6007,7 @@
         <v>52</v>
       </c>
       <c r="O17" s="8">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="P17" s="7"/>
       <c r="Q17" s="7">
@@ -5399,178 +6019,231 @@
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" s="7">
+        <v>200</v>
+      </c>
+      <c r="G18" s="8">
+        <v>0.95</v>
+      </c>
+      <c r="H18" s="7">
+        <v>210.53</v>
+      </c>
+      <c r="I18" s="8">
+        <v>1.66</v>
+      </c>
+      <c r="J18" s="8">
+        <v>1</v>
+      </c>
+      <c r="K18" s="8">
+        <v>1</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="O18" s="8">
+        <v>2.21</v>
+      </c>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7">
+        <v>210.53</v>
+      </c>
+      <c r="S18" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="10">
-        <f>SUM(F6:F17)</f>
-        <v>22195.76</v>
-      </c>
-      <c r="G18" s="9"/>
-      <c r="H18" s="10">
-        <f>SUM(H6:H17)</f>
-        <v>23621.14</v>
-      </c>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="10">
-        <f>SUM(P6:P17)</f>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="10">
+        <f>SUM(F6:F18)</f>
+        <v>22395.76</v>
+      </c>
+      <c r="G19" s="9"/>
+      <c r="H19" s="10">
+        <f>SUM(H6:H18)</f>
+        <v>23831.67</v>
+      </c>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="10">
+        <f>SUM(P6:P18)</f>
         <v>6780.57</v>
       </c>
-      <c r="Q18" s="10">
-        <f>SUM(Q6:Q17)</f>
+      <c r="Q19" s="10">
+        <f>SUM(Q6:Q18)</f>
         <v>8940</v>
       </c>
-      <c r="R18" s="10">
-        <f>SUM(R6:R17)</f>
-        <v>7900.57</v>
-      </c>
-      <c r="S18" s="9"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
+      <c r="R19" s="10">
+        <f>SUM(R6:R18)</f>
+        <v>8111.1</v>
+      </c>
+      <c r="S19" s="9"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="13">
-        <f>SUMIF(C6:C17,"&lt;&gt;Distribuição (alimentador de quadro)",H6:H17)</f>
-        <v>23621.14</v>
-      </c>
-      <c r="F21" s="13"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
       <c r="E22" s="13">
-        <f>SUMIF(C6:C17,"Distribuição (alimentador de quadro)",H6:H17)</f>
+        <f>SUMIF(C6:C18,"&lt;&gt;Distribuição (alimentador de quadro)",H6:H18)</f>
+        <v>23831.67</v>
+      </c>
+      <c r="F22" s="13"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="13">
+        <f>SUMIF(C6:C18,"Distribuição (alimentador de quadro)",H6:H18)</f>
         <v>0</v>
       </c>
-      <c r="F22" s="13"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="15">
-        <v>1</v>
-      </c>
-      <c r="F23" s="15"/>
+      <c r="F23" s="13"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
       <c r="D24" s="14"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
+      <c r="E24" s="15">
+        <v>1</v>
+      </c>
+      <c r="F24" s="15"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="13">
-        <f>IF(N(E24)&gt;0,E24*1000,E23*E21+E22)</f>
-        <v>23621.14</v>
-      </c>
-      <c r="F25" s="13"/>
+      <c r="A25" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
-      <c r="E26" s="17">
-        <f>E25/(SQRT(3)*220)</f>
-        <v>61.99</v>
-      </c>
-      <c r="F26" s="17"/>
+      <c r="E26" s="13">
+        <f>IF(N(E25)&gt;0,E25*1000,E24*E22+E23)</f>
+        <v>23831.67</v>
+      </c>
+      <c r="F26" s="13"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
-      <c r="E27" s="18">
-        <f>IF(MAX(P18,Q18,R18)&gt;0,(MAX(P18,Q18,R18)-MIN(P18,Q18,R18))/MAX(P18,Q18,R18),0)</f>
-        <v>0.24154693103938063</v>
-      </c>
-      <c r="F27" s="18"/>
+      <c r="E27" s="17">
+        <f>E26/(SQRT(3)*220)</f>
+        <v>62.54</v>
+      </c>
+      <c r="F27" s="17"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
-      <c r="E28" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="F28" s="20"/>
-    </row>
-    <row r="30" ht="26" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
+      <c r="E28" s="18">
+        <f>IF(MAX(P19,Q19,R19)&gt;0,(MAX(P19,Q19,R19)-MIN(P19,Q19,R19))/MAX(P19,Q19,R19),0)</f>
+        <v>0.24154693103938063</v>
+      </c>
+      <c r="F28" s="18"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="F29" s="20"/>
+    </row>
+    <row r="31" ht="26" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19"/>
-      <c r="O30" s="19"/>
-      <c r="P30" s="19"/>
-      <c r="Q30" s="19"/>
-      <c r="R30" s="19"/>
-      <c r="S30" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="19"/>
+      <c r="M31" s="19"/>
+      <c r="N31" s="19"/>
+      <c r="O31" s="19"/>
+      <c r="P31" s="19"/>
+      <c r="Q31" s="19"/>
+      <c r="R31" s="19"/>
+      <c r="S31" s="19"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:S17"/>
+  <autoFilter ref="A5:S18"/>
   <mergeCells count="20">
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:S3"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="E21:F21"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="E22:F22"/>
     <mergeCell ref="A23:D23"/>
@@ -5585,7 +6258,9 @@
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="A28:D28"/>
     <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A30:S30"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A31:S31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
@@ -5597,7 +6272,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z18"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -5625,7 +6300,7 @@
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5718,7 +6393,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>4</v>
@@ -5733,7 +6408,7 @@
         <v>7</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>8</v>
@@ -5748,13 +6423,13 @@
         <v>11</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>12</v>
@@ -5763,13 +6438,13 @@
         <v>13</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="R5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="T5" s="4" t="s">
         <v>15</v>
@@ -5778,19 +6453,19 @@
         <v>16</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="W5" s="3" t="s">
         <v>17</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Y5" s="3" t="s">
         <v>21</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -5798,7 +6473,7 @@
         <v>42</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>43</v>
@@ -5831,10 +6506,10 @@
         <v>24</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O6" s="8">
         <v>1</v>
@@ -5852,7 +6527,7 @@
         <v>12.25</v>
       </c>
       <c r="T6" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="U6" s="5" t="s">
         <v>29</v>
@@ -5861,16 +6536,16 @@
         <v>3.41</v>
       </c>
       <c r="W6" s="8">
-        <v>4.23</v>
+        <v>4.24</v>
       </c>
       <c r="X6" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Y6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Z6" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -5878,7 +6553,7 @@
         <v>49</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>50</v>
@@ -5911,10 +6586,10 @@
         <v>18</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O7" s="8">
         <v>1</v>
@@ -5932,25 +6607,25 @@
         <v>11.38</v>
       </c>
       <c r="T7" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="U7" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="V7" s="8">
         <v>1.77</v>
       </c>
       <c r="W7" s="8">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="X7" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Y7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Z7" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -5958,7 +6633,7 @@
         <v>53</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>54</v>
@@ -5991,10 +6666,10 @@
         <v>22</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O8" s="8">
         <v>1</v>
@@ -6012,7 +6687,7 @@
         <v>16.8</v>
       </c>
       <c r="T8" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="U8" s="5" t="s">
         <v>29</v>
@@ -6024,13 +6699,13 @@
         <v>3.56</v>
       </c>
       <c r="X8" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Y8" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Z8" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -6038,7 +6713,7 @@
         <v>59</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>60</v>
@@ -6071,10 +6746,10 @@
         <v>14</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O9" s="8">
         <v>1</v>
@@ -6092,10 +6767,10 @@
         <v>20.8</v>
       </c>
       <c r="T9" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="U9" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="U9" s="5" t="s">
-        <v>109</v>
       </c>
       <c r="V9" s="8">
         <v>1.59</v>
@@ -6104,13 +6779,13 @@
         <v>2.41</v>
       </c>
       <c r="X9" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Y9" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Z9" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
@@ -6118,7 +6793,7 @@
         <v>62</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>63</v>
@@ -6151,10 +6826,10 @@
         <v>17</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O10" s="8">
         <v>1</v>
@@ -6172,25 +6847,25 @@
         <v>20.8</v>
       </c>
       <c r="T10" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="U10" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="U10" s="5" t="s">
-        <v>109</v>
       </c>
       <c r="V10" s="8">
         <v>1.32</v>
       </c>
       <c r="W10" s="8">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="X10" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Y10" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Z10" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
@@ -6198,7 +6873,7 @@
         <v>64</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>65</v>
@@ -6231,10 +6906,10 @@
         <v>15</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O11" s="8">
         <v>1</v>
@@ -6252,25 +6927,25 @@
         <v>25.6</v>
       </c>
       <c r="T11" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="U11" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="V11" s="8">
         <v>2.02</v>
       </c>
       <c r="W11" s="8">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="X11" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Y11" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Z11" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
@@ -6278,7 +6953,7 @@
         <v>71</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>72</v>
@@ -6311,10 +6986,10 @@
         <v>21</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O12" s="8">
         <v>1</v>
@@ -6332,25 +7007,25 @@
         <v>45.6</v>
       </c>
       <c r="T12" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="U12" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="V12" s="8">
         <v>1.49</v>
       </c>
       <c r="W12" s="8">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="X12" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Y12" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Z12" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
@@ -6358,7 +7033,7 @@
         <v>77</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>78</v>
@@ -6391,10 +7066,10 @@
         <v>19</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O13" s="8">
         <v>1</v>
@@ -6412,7 +7087,7 @@
         <v>16.8</v>
       </c>
       <c r="T13" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="U13" s="5" t="s">
         <v>29</v>
@@ -6421,16 +7096,16 @@
         <v>0.98</v>
       </c>
       <c r="W13" s="8">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X13" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Y13" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Z13" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
@@ -6438,7 +7113,7 @@
         <v>81</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>82</v>
@@ -6471,10 +7146,10 @@
         <v>12</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O14" s="8">
         <v>1</v>
@@ -6492,25 +7167,25 @@
         <v>20.8</v>
       </c>
       <c r="T14" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="U14" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="U14" s="5" t="s">
-        <v>109</v>
       </c>
       <c r="V14" s="8">
         <v>1.59</v>
       </c>
       <c r="W14" s="8">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="X14" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Y14" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Z14" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
@@ -6518,7 +7193,7 @@
         <v>83</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>84</v>
@@ -6551,10 +7226,10 @@
         <v>28</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="O15" s="8">
         <v>1</v>
@@ -6572,10 +7247,10 @@
         <v>29</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="U15" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="V15" s="8">
         <v>0.68</v>
@@ -6584,13 +7259,13 @@
         <v>1.5</v>
       </c>
       <c r="X15" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Y15" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Z15" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
@@ -6598,7 +7273,7 @@
         <v>86</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>87</v>
@@ -6631,10 +7306,10 @@
         <v>20</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="O16" s="8">
         <v>1</v>
@@ -6652,25 +7327,25 @@
         <v>14</v>
       </c>
       <c r="T16" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="U16" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="V16" s="8">
         <v>1.09</v>
       </c>
       <c r="W16" s="8">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="X16" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Y16" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Z16" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
@@ -6678,7 +7353,7 @@
         <v>88</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>89</v>
@@ -6711,10 +7386,10 @@
         <v>22</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="O17" s="8">
         <v>1</v>
@@ -6732,69 +7407,69 @@
         <v>19.2</v>
       </c>
       <c r="T17" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="U17" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="V17" s="8">
         <v>1.26</v>
       </c>
       <c r="W17" s="8">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="X17" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Y17" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Z17" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="G18" s="21">
-        <v>220</v>
+        <v>127</v>
       </c>
       <c r="H18" s="7">
-        <v>22195.76</v>
+        <v>200</v>
       </c>
       <c r="I18" s="8">
-        <v>0.94</v>
+        <v>0.95</v>
       </c>
       <c r="J18" s="7">
-        <v>23621.14</v>
+        <v>210.53</v>
       </c>
       <c r="K18" s="8">
-        <v>61.99</v>
+        <v>1.66</v>
       </c>
       <c r="L18" s="22">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N18" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="O18" s="8">
         <v>1</v>
@@ -6806,22 +7481,22 @@
         <v>1</v>
       </c>
       <c r="R18" s="5" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="S18" s="22">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="T18" s="6" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="U18" s="5" t="s">
-        <v>29</v>
+        <v>111</v>
       </c>
       <c r="V18" s="8">
-        <v>0.82</v>
+        <v>1.39</v>
       </c>
       <c r="W18" s="8">
-        <v>0.82</v>
+        <v>2.21</v>
       </c>
       <c r="X18" s="6" t="s">
         <v>122</v>
@@ -6830,11 +7505,91 @@
         <v>30</v>
       </c>
       <c r="Z18" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="21">
+        <v>220</v>
+      </c>
+      <c r="H19" s="7">
+        <v>22395.76</v>
+      </c>
+      <c r="I19" s="8">
+        <v>0.94</v>
+      </c>
+      <c r="J19" s="7">
+        <v>23831.67</v>
+      </c>
+      <c r="K19" s="8">
+        <v>62.54</v>
+      </c>
+      <c r="L19" s="22">
+        <v>12</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="N19" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="O19" s="8">
+        <v>1</v>
+      </c>
+      <c r="P19" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="23">
+        <v>1</v>
+      </c>
+      <c r="R19" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S19" s="22">
+        <v>67</v>
+      </c>
+      <c r="T19" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="U19" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="V19" s="8">
+        <v>0.83</v>
+      </c>
+      <c r="W19" s="8">
+        <v>0.83</v>
+      </c>
+      <c r="X19" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y19" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z19" s="6" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:Z18"/>
+  <autoFilter ref="A5:Z19"/>
   <mergeCells count="3">
     <mergeCell ref="A1:Z1"/>
     <mergeCell ref="A2:Z2"/>
@@ -6847,7 +7602,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -6864,7 +7619,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6915,51 +7670,51 @@
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C6" s="21">
         <v>9</v>
@@ -6974,7 +7729,7 @@
         <v>16.18</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H6" s="22">
         <v>21</v>
@@ -6992,15 +7747,15 @@
         <v>30</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C7" s="21">
         <v>12</v>
@@ -7015,7 +7770,7 @@
         <v>21.55</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H7" s="22">
         <v>26.8</v>
@@ -7033,15 +7788,15 @@
         <v>30</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C8" s="21">
         <v>6</v>
@@ -7056,7 +7811,7 @@
         <v>20.28</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H8" s="22">
         <v>21</v>
@@ -7074,12 +7829,12 @@
         <v>30</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>83</v>
@@ -7097,7 +7852,7 @@
         <v>16.16</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H9" s="22">
         <v>21</v>
@@ -7113,36 +7868,36 @@
         <v>30</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="C10" s="21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D10" s="22">
-        <v>354.41</v>
+        <v>68.71</v>
       </c>
       <c r="E10" s="24">
         <v>0.4</v>
       </c>
       <c r="F10" s="22">
-        <v>33.59</v>
+        <v>14.79</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>122</v>
       </c>
       <c r="H10" s="22">
-        <v>35</v>
+        <v>16.1</v>
       </c>
       <c r="I10" s="25">
-        <v>0.36836734693877543</v>
+        <v>0.3374869796689942</v>
       </c>
       <c r="J10" s="22"/>
       <c r="K10" s="21">
@@ -7152,11 +7907,50 @@
         <v>30</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="21">
+        <v>5</v>
+      </c>
+      <c r="D11" s="22">
+        <v>354.41</v>
+      </c>
+      <c r="E11" s="24">
+        <v>0.4</v>
+      </c>
+      <c r="F11" s="22">
+        <v>33.59</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H11" s="22">
+        <v>35</v>
+      </c>
+      <c r="I11" s="25">
+        <v>0.36836734693877543</v>
+      </c>
+      <c r="J11" s="22"/>
+      <c r="K11" s="21">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:M10"/>
+  <autoFilter ref="A5:M11"/>
   <mergeCells count="3">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
@@ -7189,7 +7983,7 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7255,69 +8049,69 @@
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D6" s="21">
         <v>6</v>
@@ -7338,7 +8132,7 @@
         <v>4.08</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="K6" s="25">
         <v>0.035832431443645354</v>
@@ -7362,7 +8156,7 @@
         <v>30</v>
       </c>
       <c r="R6" s="6" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -7401,7 +8195,7 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7482,81 +8276,81 @@
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="V5" s="3" t="s">
         <v>21</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C6" s="8">
         <v>16.2</v>
@@ -7571,7 +8365,7 @@
         <v>80</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H6" s="22">
         <v>18</v>
@@ -7595,7 +8389,7 @@
         <v>4</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="P6" s="21">
         <v>170</v>
@@ -7619,15 +8413,15 @@
         <v>30</v>
       </c>
       <c r="W6" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C7" s="8">
         <v>10.2</v>
@@ -7642,7 +8436,7 @@
         <v>80</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H7" s="22">
         <v>18</v>
@@ -7666,7 +8460,7 @@
         <v>4</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="P7" s="21">
         <v>217</v>
@@ -7690,15 +8484,15 @@
         <v>30</v>
       </c>
       <c r="W7" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C8" s="8">
         <v>8.96</v>
@@ -7713,7 +8507,7 @@
         <v>80</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H8" s="22">
         <v>12</v>
@@ -7737,7 +8531,7 @@
         <v>8</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="P8" s="21">
         <v>336</v>
@@ -7761,15 +8555,15 @@
         <v>30</v>
       </c>
       <c r="W8" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C9" s="8">
         <v>8.32</v>
@@ -7784,7 +8578,7 @@
         <v>80</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="H9" s="22">
         <v>17.5</v>
@@ -7808,7 +8602,7 @@
         <v>6</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="P9" s="21">
         <v>690</v>
@@ -7829,10 +8623,10 @@
         <v>42</v>
       </c>
       <c r="V9" s="5" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="W9" s="6" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
@@ -7884,6 +8678,293 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Z6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="4" width="7" customWidth="1"/>
+    <col min="7" max="7" width="7" customWidth="1"/>
+    <col min="8" max="8" width="36" customWidth="1"/>
+    <col min="9" max="9" width="7" customWidth="1"/>
+    <col min="11" max="11" width="7" customWidth="1"/>
+    <col min="12" max="12" width="30" customWidth="1"/>
+    <col min="13" max="13" width="7" customWidth="1"/>
+    <col min="14" max="14" width="6" customWidth="1"/>
+    <col min="15" max="15" width="7" customWidth="1"/>
+    <col min="16" max="17" width="6" customWidth="1"/>
+    <col min="18" max="18" width="7" customWidth="1"/>
+    <col min="19" max="19" width="5" customWidth="1"/>
+    <col min="22" max="22" width="6" customWidth="1"/>
+    <col min="24" max="24" width="8" customWidth="1"/>
+    <col min="25" max="25" width="14" customWidth="1"/>
+    <col min="26" max="26" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2"/>
+      <c r="Z3" s="2"/>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="W5" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="X5" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="Y5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z5" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C6" s="22">
+        <v>30</v>
+      </c>
+      <c r="D6" s="22">
+        <v>18</v>
+      </c>
+      <c r="E6" s="7">
+        <v>540</v>
+      </c>
+      <c r="F6" s="21">
+        <v>10</v>
+      </c>
+      <c r="G6" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="I6" s="21">
+        <v>50</v>
+      </c>
+      <c r="J6" s="7">
+        <v>5000</v>
+      </c>
+      <c r="K6" s="21">
+        <v>120</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="M6" s="21">
+        <v>4</v>
+      </c>
+      <c r="N6" s="22">
+        <v>7</v>
+      </c>
+      <c r="O6" s="21">
+        <v>40</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0.45</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="R6" s="8">
+        <v>3</v>
+      </c>
+      <c r="S6" s="21">
+        <v>4</v>
+      </c>
+      <c r="T6" s="21">
+        <v>14</v>
+      </c>
+      <c r="U6" s="21">
+        <v>7</v>
+      </c>
+      <c r="V6" s="8">
+        <v>0.51</v>
+      </c>
+      <c r="W6" s="7">
+        <v>200</v>
+      </c>
+      <c r="X6" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z6" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:Z6"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="A2:Z2"/>
+    <mergeCell ref="A3:Z3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -7912,7 +8993,7 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8005,108 +9086,108 @@
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="R5" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="Y5" s="3" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="Z5" s="3" t="s">
         <v>21</v>
       </c>
       <c r="AA5" s="4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="H6" s="23">
         <v>23.688</v>
@@ -8141,39 +9222,39 @@
         <v>20.11</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="U6" s="6" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="V6" s="6" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="W6" s="6" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="X6" s="5" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="Y6" s="5" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="Z6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="AA6" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="B9" s="28"/>
       <c r="C9" s="28"/>
@@ -8215,7 +9296,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -8230,7 +9311,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8266,48 +9347,48 @@
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="E6" s="21">
         <v>1</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="G6" s="23">
         <v>1.49</v>
@@ -8319,22 +9400,22 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="E7" s="21">
         <v>1</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="G7" s="23">
         <v>4.08</v>
@@ -8346,22 +9427,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="E8" s="21">
         <v>1</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="G8" s="23">
         <v>5.5</v>
@@ -8373,22 +9454,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="E9" s="21">
         <v>1</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="G9" s="23">
         <v>7.5</v>
@@ -8400,22 +9481,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="E10" s="21">
         <v>1</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="G10" s="23">
         <v>1.26</v>
@@ -8427,22 +9508,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="E11" s="21">
         <v>1</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="G11" s="23">
         <v>1.8</v>
@@ -8454,22 +9535,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="E12" s="21">
         <v>1</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="G12" s="23">
         <v>1.398</v>
@@ -8481,22 +9562,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>271</v>
+        <v>294</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="E13" s="21">
         <v>1</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="G13" s="23">
         <v>0.66</v>
@@ -8516,339 +9597,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:P9"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="4" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="7" customWidth="1"/>
-    <col min="8" max="10" width="8" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="7" customWidth="1"/>
-    <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="22" customWidth="1"/>
-    <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="50" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="B6" s="8">
-        <v>10.2</v>
-      </c>
-      <c r="C6" s="21">
-        <v>2</v>
-      </c>
-      <c r="D6" s="7">
-        <v>2303</v>
-      </c>
-      <c r="E6" s="7">
-        <v>63</v>
-      </c>
-      <c r="F6" s="7">
-        <f>D6+E6</f>
-        <v>2366</v>
-      </c>
-      <c r="G6" s="8">
-        <v>0.97</v>
-      </c>
-      <c r="H6" s="21">
-        <v>17</v>
-      </c>
-      <c r="I6" s="21">
-        <v>232</v>
-      </c>
-      <c r="J6" s="24">
-        <v>0.1</v>
-      </c>
-      <c r="K6" s="7">
-        <f>F6*(1+J6)*3.412142</f>
-        <v>8879</v>
-      </c>
-      <c r="L6" s="8">
-        <f>F6*(1+J6)/3516.85</f>
-        <v>0.74</v>
-      </c>
-      <c r="M6" s="22">
-        <v>0</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="O6" s="7">
-        <v>824</v>
-      </c>
-      <c r="P6" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="B7" s="8">
-        <v>16.2</v>
-      </c>
-      <c r="C7" s="21">
-        <v>4</v>
-      </c>
-      <c r="D7" s="7">
-        <v>2456</v>
-      </c>
-      <c r="E7" s="7">
-        <v>280</v>
-      </c>
-      <c r="F7" s="7">
-        <f>D7+E7</f>
-        <v>2736</v>
-      </c>
-      <c r="G7" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="H7" s="21">
-        <v>15</v>
-      </c>
-      <c r="I7" s="21">
-        <v>169</v>
-      </c>
-      <c r="J7" s="24">
-        <v>0.1</v>
-      </c>
-      <c r="K7" s="7">
-        <f>F7*(1+J7)*3.412142</f>
-        <v>10270</v>
-      </c>
-      <c r="L7" s="8">
-        <f>F7*(1+J7)/3516.85</f>
-        <v>0.86</v>
-      </c>
-      <c r="M7" s="22">
-        <v>0</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="O7" s="7">
-        <v>1099</v>
-      </c>
-      <c r="P7" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="B8" s="8">
-        <v>8.32</v>
-      </c>
-      <c r="C8" s="21">
-        <v>1</v>
-      </c>
-      <c r="D8" s="7">
-        <v>2096</v>
-      </c>
-      <c r="E8" s="7">
-        <v>137</v>
-      </c>
-      <c r="F8" s="7">
-        <f>D8+E8</f>
-        <v>2234</v>
-      </c>
-      <c r="G8" s="8">
-        <v>0.94</v>
-      </c>
-      <c r="H8" s="21">
-        <v>16</v>
-      </c>
-      <c r="I8" s="21">
-        <v>268</v>
-      </c>
-      <c r="J8" s="24">
-        <v>0.1</v>
-      </c>
-      <c r="K8" s="7">
-        <f>F8*(1+J8)*3.412142</f>
-        <v>8383</v>
-      </c>
-      <c r="L8" s="8">
-        <f>F8*(1+J8)/3516.85</f>
-        <v>0.7</v>
-      </c>
-      <c r="M8" s="22">
-        <v>5</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="O8" s="7">
-        <v>824</v>
-      </c>
-      <c r="P8" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="B9" s="26">
-        <f>SUM(B6:B8)</f>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="10">
-        <f>SUM(D6:D8)</f>
-      </c>
-      <c r="E9" s="10">
-        <f>SUM(E6:E8)</f>
-      </c>
-      <c r="F9" s="10">
-        <f>SUM(F6:F8)</f>
-      </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="10">
-        <f>SUM(K6:K8)</f>
-      </c>
-      <c r="L9" s="26">
-        <f>SUM(L6:L8)</f>
-      </c>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="10">
-        <f>SUM(O6:O8)</f>
-      </c>
-      <c r="P9" s="9"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A5:P8"/>
-  <mergeCells count="3">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A2:P2"/>
-    <mergeCell ref="A3:P3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
-</worksheet>
 </file>
--- a/exemplo/quadro-de-cargas-residencia-unifamiliar-exemplo-r00.xlsx
+++ b/exemplo/quadro-de-cargas-residencia-unifamiliar-exemplo-r00.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="459">
   <si>
     <t>Quadro de cargas — QM — Quadro de medição (ponto de entrega)</t>
   </si>
@@ -1164,6 +1164,15 @@
     <t>Dispositivos de proteção</t>
   </si>
   <si>
+    <t>DPS classe II — Uc 175 V, In 20 kA, Imáx 40 kA</t>
+  </si>
+  <si>
+    <t>ABNT NBR IEC 61643-11</t>
+  </si>
+  <si>
+    <t>QM, QD-1</t>
+  </si>
+  <si>
     <t>Disjuntor termomagnético 1P curva C 10 A — 6,0 kA</t>
   </si>
   <si>
@@ -1207,9 +1216,6 @@
   </si>
   <si>
     <t>DPS classe II — 275 V, In 20 kA, Imáx 40 kA</t>
-  </si>
-  <si>
-    <t>ABNT NBR IEC 61643-11</t>
   </si>
   <si>
     <t>cadastro</t>
@@ -3187,7 +3193,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -4113,7 +4119,7 @@
         <v>332</v>
       </c>
       <c r="G38" s="29">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>382</v>
@@ -4130,7 +4136,7 @@
         <v>383</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>110</v>
@@ -4139,10 +4145,10 @@
         <v>332</v>
       </c>
       <c r="G39" s="29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -4153,10 +4159,10 @@
         <v>379</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>110</v>
@@ -4165,10 +4171,10 @@
         <v>332</v>
       </c>
       <c r="G40" s="29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -4179,10 +4185,10 @@
         <v>379</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>110</v>
@@ -4191,10 +4197,10 @@
         <v>332</v>
       </c>
       <c r="G41" s="29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>64</v>
+        <v>389</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -4205,10 +4211,10 @@
         <v>379</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>110</v>
@@ -4220,7 +4226,7 @@
         <v>1</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -4231,10 +4237,10 @@
         <v>379</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>110</v>
@@ -4246,7 +4252,7 @@
         <v>1</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -4257,10 +4263,10 @@
         <v>379</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>110</v>
@@ -4269,10 +4275,10 @@
         <v>332</v>
       </c>
       <c r="G44" s="29">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>392</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -4286,7 +4292,7 @@
         <v>393</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>110</v>
@@ -4295,10 +4301,10 @@
         <v>332</v>
       </c>
       <c r="G45" s="29">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>71</v>
+        <v>395</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -4309,10 +4315,10 @@
         <v>379</v>
       </c>
       <c r="C46" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="D46" s="6" t="s">
         <v>394</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>395</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>110</v>
@@ -4321,10 +4327,10 @@
         <v>332</v>
       </c>
       <c r="G46" s="29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>396</v>
+        <v>71</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -4332,13 +4338,13 @@
         <v>42</v>
       </c>
       <c r="B47" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="C47" s="6" t="s">
         <v>397</v>
       </c>
-      <c r="C47" s="6" t="s">
-        <v>398</v>
-      </c>
       <c r="D47" s="6" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>110</v>
@@ -4347,10 +4353,10 @@
         <v>332</v>
       </c>
       <c r="G47" s="29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>105</v>
+        <v>398</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -4358,13 +4364,13 @@
         <v>43</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>400</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>110</v>
@@ -4376,7 +4382,7 @@
         <v>1</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>396</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -4384,13 +4390,13 @@
         <v>44</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C49" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="D49" s="6" t="s">
         <v>401</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>399</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>110</v>
@@ -4402,7 +4408,7 @@
         <v>1</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -4410,25 +4416,25 @@
         <v>45</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>403</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="G50" s="29">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -4436,13 +4442,13 @@
         <v>46</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C51" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="D51" s="6" t="s">
         <v>406</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>404</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>110</v>
@@ -4451,7 +4457,7 @@
         <v>341</v>
       </c>
       <c r="G51" s="29">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>407</v>
@@ -4462,13 +4468,13 @@
         <v>47</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>408</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>110</v>
@@ -4477,7 +4483,7 @@
         <v>341</v>
       </c>
       <c r="G52" s="29">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>409</v>
@@ -4488,13 +4494,13 @@
         <v>48</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>410</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>110</v>
@@ -4503,7 +4509,7 @@
         <v>341</v>
       </c>
       <c r="G53" s="29">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>411</v>
@@ -4514,13 +4520,13 @@
         <v>49</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>412</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>110</v>
@@ -4532,7 +4538,7 @@
         <v>14</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -4540,25 +4546,25 @@
         <v>50</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C55" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="D55" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="D55" s="6" t="s">
-        <v>413</v>
-      </c>
       <c r="E55" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="G55" s="29">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -4566,13 +4572,13 @@
         <v>51</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>417</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>110</v>
@@ -4581,10 +4587,10 @@
         <v>332</v>
       </c>
       <c r="G56" s="29">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -4592,13 +4598,13 @@
         <v>52</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>419</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>110</v>
@@ -4607,10 +4613,10 @@
         <v>332</v>
       </c>
       <c r="G57" s="29">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -4618,13 +4624,13 @@
         <v>53</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>421</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>110</v>
@@ -4633,10 +4639,10 @@
         <v>332</v>
       </c>
       <c r="G58" s="29">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -4644,13 +4650,13 @@
         <v>54</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>423</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>110</v>
@@ -4659,10 +4665,10 @@
         <v>332</v>
       </c>
       <c r="G59" s="29">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -4670,13 +4676,13 @@
         <v>55</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C60" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="D60" s="6" t="s">
         <v>424</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>425</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>110</v>
@@ -4685,10 +4691,10 @@
         <v>332</v>
       </c>
       <c r="G60" s="29">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -4696,13 +4702,13 @@
         <v>56</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>426</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E61" s="6" t="s">
         <v>110</v>
@@ -4711,10 +4717,10 @@
         <v>332</v>
       </c>
       <c r="G61" s="29">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -4722,13 +4728,13 @@
         <v>57</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C62" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D62" s="6" t="s">
         <v>427</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>418</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>110</v>
@@ -4737,10 +4743,10 @@
         <v>332</v>
       </c>
       <c r="G62" s="29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -4748,13 +4754,13 @@
         <v>58</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>44</v>
+        <v>422</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>110</v>
@@ -4763,10 +4769,10 @@
         <v>332</v>
       </c>
       <c r="G63" s="29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>186</v>
+        <v>398</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -4780,7 +4786,7 @@
         <v>430</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>110</v>
@@ -4792,7 +4798,7 @@
         <v>4</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -4803,10 +4809,10 @@
         <v>44</v>
       </c>
       <c r="C65" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="D65" s="6" t="s">
         <v>431</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>429</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>110</v>
@@ -4815,10 +4821,10 @@
         <v>332</v>
       </c>
       <c r="G65" s="29">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -4829,10 +4835,10 @@
         <v>44</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>110</v>
@@ -4841,10 +4847,10 @@
         <v>332</v>
       </c>
       <c r="G66" s="29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -4855,10 +4861,10 @@
         <v>44</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E67" s="6" t="s">
         <v>110</v>
@@ -4867,10 +4873,10 @@
         <v>332</v>
       </c>
       <c r="G67" s="29">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -4919,7 +4925,7 @@
         <v>332</v>
       </c>
       <c r="G69" s="29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H69" s="6" t="s">
         <v>218</v>
@@ -4930,13 +4936,13 @@
         <v>65</v>
       </c>
       <c r="B70" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C70" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="C70" s="6" t="s">
+      <c r="D70" s="6" t="s">
         <v>440</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>441</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>110</v>
@@ -4945,10 +4951,10 @@
         <v>332</v>
       </c>
       <c r="G70" s="29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>442</v>
+        <v>218</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -4956,13 +4962,13 @@
         <v>66</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C71" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="D71" s="6" t="s">
         <v>443</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>444</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>110</v>
@@ -4974,7 +4980,7 @@
         <v>4</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -4982,13 +4988,13 @@
         <v>67</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>445</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>110</v>
+        <v>446</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>110</v>
@@ -5000,7 +5006,7 @@
         <v>4</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -5008,25 +5014,25 @@
         <v>68</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D73" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="G73" s="29">
+        <v>4</v>
+      </c>
+      <c r="H73" s="6" t="s">
         <v>444</v>
-      </c>
-      <c r="E73" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="F73" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="G73" s="29">
-        <v>8</v>
-      </c>
-      <c r="H73" s="6" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -5034,13 +5040,13 @@
         <v>69</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>110</v>
@@ -5049,10 +5055,10 @@
         <v>341</v>
       </c>
       <c r="G74" s="29">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -5060,13 +5066,13 @@
         <v>70</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>404</v>
+        <v>446</v>
       </c>
       <c r="E75" s="6" t="s">
         <v>110</v>
@@ -5078,7 +5084,7 @@
         <v>3</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -5086,25 +5092,25 @@
         <v>71</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>450</v>
+        <v>406</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="G76" s="29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>396</v>
+        <v>444</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -5112,13 +5118,13 @@
         <v>72</v>
       </c>
       <c r="B77" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="C77" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="C77" s="6" t="s">
+      <c r="D77" s="6" t="s">
         <v>452</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>110</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>110</v>
@@ -5127,10 +5133,10 @@
         <v>332</v>
       </c>
       <c r="G77" s="29">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -5138,10 +5144,10 @@
         <v>73</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>110</v>
@@ -5150,13 +5156,13 @@
         <v>110</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>454</v>
+        <v>332</v>
       </c>
       <c r="G78" s="29">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -5164,7 +5170,7 @@
         <v>74</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>455</v>
@@ -5179,14 +5185,40 @@
         <v>456</v>
       </c>
       <c r="G79" s="29">
+        <v>5</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="5">
+        <v>75</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="G80" s="29">
         <v>1</v>
       </c>
-      <c r="H79" s="6" t="s">
-        <v>396</v>
+      <c r="H80" s="6" t="s">
+        <v>398</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:H79"/>
+  <autoFilter ref="A5:H80"/>
   <mergeCells count="3">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>

--- a/exemplo/quadro-de-cargas-residencia-unifamiliar-exemplo-r00.xlsx
+++ b/exemplo/quadro-de-cargas-residencia-unifamiliar-exemplo-r00.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="476">
   <si>
     <t>Quadro de cargas — QM — Quadro de medição (ponto de entrega)</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Obra: Residência unifamiliar — exemplo — Proprietário (exemplo)</t>
   </si>
   <si>
-    <t>Sistema: 127/220 V, trifásico, esquema TN-S · Responsável: Nome do responsável técnico — CREA/CFT nº 000000 · R00 · 26/10/2026</t>
+    <t>Sistema: 127/220 V, trifásico, esquema TN-S · Responsável: Nome do responsável técnico — CREA/CFT nº 000000 · R00 · 27/10/2026</t>
   </si>
   <si>
     <t>Circ.</t>
@@ -1164,15 +1164,18 @@
     <t>Dispositivos de proteção</t>
   </si>
   <si>
+    <t>DPS classe I+II — Uc 175 V, Iimp 12,5 kA (10/350 µs), In 20 kA</t>
+  </si>
+  <si>
+    <t>ABNT NBR IEC 61643-11; NBR 5419-4</t>
+  </si>
+  <si>
     <t>DPS classe II — Uc 175 V, In 20 kA, Imáx 40 kA</t>
   </si>
   <si>
     <t>ABNT NBR IEC 61643-11</t>
   </si>
   <si>
-    <t>QM, QD-1</t>
-  </si>
-  <si>
     <t>Disjuntor termomagnético 1P curva C 10 A — 6,0 kA</t>
   </si>
   <si>
@@ -1347,6 +1350,57 @@
     <t>ABNT NBR 5123</t>
   </si>
   <si>
+    <t>SPDA — proteção contra descargas atmosféricas</t>
+  </si>
+  <si>
+    <t>Barra chata ou cabo de alumínio 70 mm² — captação (malha e perímetro da cobertura)</t>
+  </si>
+  <si>
+    <t>ABNT NBR 5419-3</t>
+  </si>
+  <si>
+    <t>SPDA</t>
+  </si>
+  <si>
+    <t>Barra chata ou cabo de alumínio 70 mm² — descidas</t>
+  </si>
+  <si>
+    <t>Cabo de cobre nu 50 mm² (7 ou 19 fios) — anel de aterramento a 0,5 m de profundidade e 1,0 m das paredes</t>
+  </si>
+  <si>
+    <t>ABNT NBR 5419-3; NBR 6524</t>
+  </si>
+  <si>
+    <t>Suporte isolador ou fixador para condutor da captação (a cada 1 m)</t>
+  </si>
+  <si>
+    <t>Fixador para condutor de descida (a cada 1 m até 20 m e 0,5 m acima)</t>
+  </si>
+  <si>
+    <t>Conector de cruzamento e emenda da malha de captação</t>
+  </si>
+  <si>
+    <t>Conector de medição (desconexão para ensaio) em cada descida</t>
+  </si>
+  <si>
+    <t>Eletroduto de PVC rígido para proteção mecânica da descida junto ao solo (2,5 m por descida)</t>
+  </si>
+  <si>
+    <t>Caixa de inspeção do aterramento (ligação descida/anel)</t>
+  </si>
+  <si>
+    <t>Conexão por solda exotérmica ou conector de compressão (descida/anel e eletrodos)</t>
+  </si>
+  <si>
+    <t>ABNT NBR 16254</t>
+  </si>
+  <si>
+    <t>Ligação do anel de aterramento ao barramento de equipotencialização principal (BEP)</t>
+  </si>
+  <si>
+    <t>ABNT NBR 5419-3; NBR 5410</t>
+  </si>
+  <si>
     <t>Aterramento e equipotencialização</t>
   </si>
   <si>
@@ -1360,9 +1414,6 @@
   </si>
   <si>
     <t>Conector cabo–haste (cunha, grampo ou solda exotérmica)</t>
-  </si>
-  <si>
-    <t>ABNT NBR 16254</t>
   </si>
   <si>
     <t>Caixa de inspeção de aterramento com tampa</t>
@@ -3193,7 +3244,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -4119,10 +4170,10 @@
         <v>332</v>
       </c>
       <c r="G38" s="29">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>382</v>
+        <v>123</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -4133,10 +4184,10 @@
         <v>379</v>
       </c>
       <c r="C39" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="D39" s="6" t="s">
         <v>383</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>384</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>110</v>
@@ -4145,10 +4196,10 @@
         <v>332</v>
       </c>
       <c r="G39" s="29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>385</v>
+        <v>105</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -4159,10 +4210,10 @@
         <v>379</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>110</v>
@@ -4171,10 +4222,10 @@
         <v>332</v>
       </c>
       <c r="G40" s="29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -4185,10 +4236,10 @@
         <v>379</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>110</v>
@@ -4197,10 +4248,10 @@
         <v>332</v>
       </c>
       <c r="G41" s="29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -4211,10 +4262,10 @@
         <v>379</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>110</v>
@@ -4223,10 +4274,10 @@
         <v>332</v>
       </c>
       <c r="G42" s="29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>64</v>
+        <v>390</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -4240,7 +4291,7 @@
         <v>391</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>110</v>
@@ -4252,7 +4303,7 @@
         <v>1</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -4266,7 +4317,7 @@
         <v>392</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>110</v>
@@ -4278,7 +4329,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -4292,7 +4343,7 @@
         <v>393</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>110</v>
@@ -4301,10 +4352,10 @@
         <v>332</v>
       </c>
       <c r="G45" s="29">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>395</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -4315,10 +4366,10 @@
         <v>379</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>110</v>
@@ -4327,10 +4378,10 @@
         <v>332</v>
       </c>
       <c r="G46" s="29">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>71</v>
+        <v>396</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -4344,7 +4395,7 @@
         <v>397</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>110</v>
@@ -4353,10 +4404,10 @@
         <v>332</v>
       </c>
       <c r="G47" s="29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>398</v>
+        <v>71</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -4364,13 +4415,13 @@
         <v>43</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>399</v>
+        <v>379</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>110</v>
@@ -4379,10 +4430,10 @@
         <v>332</v>
       </c>
       <c r="G48" s="29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>105</v>
+        <v>399</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -4390,13 +4441,13 @@
         <v>44</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C49" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="D49" s="6" t="s">
         <v>402</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>401</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>110</v>
@@ -4408,7 +4459,7 @@
         <v>1</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>398</v>
+        <v>105</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -4416,13 +4467,13 @@
         <v>45</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>403</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>110</v>
@@ -4434,7 +4485,7 @@
         <v>1</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -4442,25 +4493,25 @@
         <v>46</v>
       </c>
       <c r="B51" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="C51" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="C51" s="6" t="s">
-        <v>405</v>
-      </c>
       <c r="D51" s="6" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="G51" s="29">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -4468,13 +4519,13 @@
         <v>47</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>110</v>
@@ -4483,10 +4534,10 @@
         <v>341</v>
       </c>
       <c r="G52" s="29">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -4494,13 +4545,13 @@
         <v>48</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>110</v>
@@ -4509,10 +4560,10 @@
         <v>341</v>
       </c>
       <c r="G53" s="29">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -4520,13 +4571,13 @@
         <v>49</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>110</v>
@@ -4535,10 +4586,10 @@
         <v>341</v>
       </c>
       <c r="G54" s="29">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -4546,13 +4597,13 @@
         <v>50</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>110</v>
@@ -4564,7 +4615,7 @@
         <v>14</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -4572,25 +4623,25 @@
         <v>51</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C56" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="G56" s="29">
+        <v>14</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>417</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="F56" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="G56" s="29">
-        <v>9</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -4598,13 +4649,13 @@
         <v>52</v>
       </c>
       <c r="B57" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="C57" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="C57" s="6" t="s">
-        <v>419</v>
-      </c>
       <c r="D57" s="6" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>110</v>
@@ -4613,10 +4664,10 @@
         <v>332</v>
       </c>
       <c r="G57" s="29">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>398</v>
+        <v>417</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -4624,13 +4675,13 @@
         <v>53</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C58" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="D58" s="6" t="s">
         <v>421</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>420</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>110</v>
@@ -4639,10 +4690,10 @@
         <v>332</v>
       </c>
       <c r="G58" s="29">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -4650,13 +4701,13 @@
         <v>54</v>
       </c>
       <c r="B59" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="C59" s="6" t="s">
         <v>422</v>
       </c>
-      <c r="C59" s="6" t="s">
-        <v>423</v>
-      </c>
       <c r="D59" s="6" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>110</v>
@@ -4665,10 +4716,10 @@
         <v>332</v>
       </c>
       <c r="G59" s="29">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -4676,13 +4727,13 @@
         <v>55</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C60" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="D60" s="6" t="s">
         <v>425</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>424</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>110</v>
@@ -4691,10 +4742,10 @@
         <v>332</v>
       </c>
       <c r="G60" s="29">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -4702,13 +4753,13 @@
         <v>56</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>426</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E61" s="6" t="s">
         <v>110</v>
@@ -4717,10 +4768,10 @@
         <v>332</v>
       </c>
       <c r="G61" s="29">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -4728,13 +4779,13 @@
         <v>57</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C62" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="D62" s="6" t="s">
         <v>428</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>427</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>110</v>
@@ -4743,10 +4794,10 @@
         <v>332</v>
       </c>
       <c r="G62" s="29">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -4754,13 +4805,13 @@
         <v>58</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>429</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>110</v>
@@ -4769,10 +4820,10 @@
         <v>332</v>
       </c>
       <c r="G63" s="29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -4780,13 +4831,13 @@
         <v>59</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>44</v>
+        <v>423</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>430</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>110</v>
@@ -4795,10 +4846,10 @@
         <v>332</v>
       </c>
       <c r="G64" s="29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>186</v>
+        <v>399</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -4809,10 +4860,10 @@
         <v>44</v>
       </c>
       <c r="C65" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="D65" s="6" t="s">
         <v>432</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>431</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>110</v>
@@ -4824,7 +4875,7 @@
         <v>4</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -4838,7 +4889,7 @@
         <v>433</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>110</v>
@@ -4847,10 +4898,10 @@
         <v>332</v>
       </c>
       <c r="G66" s="29">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -4864,7 +4915,7 @@
         <v>434</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E67" s="6" t="s">
         <v>110</v>
@@ -4873,10 +4924,10 @@
         <v>332</v>
       </c>
       <c r="G67" s="29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -4890,7 +4941,7 @@
         <v>435</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>110</v>
@@ -4899,10 +4950,10 @@
         <v>332</v>
       </c>
       <c r="G68" s="29">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -4913,10 +4964,10 @@
         <v>44</v>
       </c>
       <c r="C69" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="D69" s="6" t="s">
         <v>437</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>438</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>110</v>
@@ -4939,10 +4990,10 @@
         <v>44</v>
       </c>
       <c r="C70" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="D70" s="6" t="s">
         <v>439</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>440</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>110</v>
@@ -4951,7 +5002,7 @@
         <v>332</v>
       </c>
       <c r="G70" s="29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>218</v>
@@ -4962,13 +5013,13 @@
         <v>66</v>
       </c>
       <c r="B71" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="D71" s="6" t="s">
         <v>441</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>442</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>443</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>110</v>
@@ -4977,10 +5028,10 @@
         <v>332</v>
       </c>
       <c r="G71" s="29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>444</v>
+        <v>218</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -4988,25 +5039,25 @@
         <v>67</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C72" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="G72" s="29">
+        <v>49</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>445</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="E72" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="F72" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="G72" s="29">
-        <v>4</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -5014,25 +5065,25 @@
         <v>68</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>110</v>
+        <v>444</v>
       </c>
       <c r="E73" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="G73" s="29">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -5040,13 +5091,13 @@
         <v>69</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C74" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="D74" s="6" t="s">
         <v>448</v>
-      </c>
-      <c r="D74" s="6" t="s">
-        <v>446</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>110</v>
@@ -5055,10 +5106,10 @@
         <v>341</v>
       </c>
       <c r="G74" s="29">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -5066,25 +5117,25 @@
         <v>70</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>449</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E75" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="G75" s="29">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -5092,25 +5143,25 @@
         <v>71</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>450</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>406</v>
+        <v>444</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="G76" s="29">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -5118,13 +5169,13 @@
         <v>72</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>451</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>110</v>
@@ -5133,10 +5184,10 @@
         <v>332</v>
       </c>
       <c r="G77" s="29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>398</v>
+        <v>445</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -5144,13 +5195,13 @@
         <v>73</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>110</v>
+        <v>444</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>110</v>
@@ -5159,10 +5210,10 @@
         <v>332</v>
       </c>
       <c r="G78" s="29">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>398</v>
+        <v>445</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -5170,25 +5221,25 @@
         <v>74</v>
       </c>
       <c r="B79" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="C79" s="6" t="s">
         <v>453</v>
       </c>
-      <c r="C79" s="6" t="s">
-        <v>455</v>
-      </c>
       <c r="D79" s="6" t="s">
-        <v>110</v>
+        <v>407</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>456</v>
+        <v>341</v>
       </c>
       <c r="G79" s="29">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>398</v>
+        <v>445</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -5196,29 +5247,341 @@
         <v>75</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="C80" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="G80" s="29">
+        <v>4</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="5">
+        <v>76</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="G81" s="29">
+        <v>4</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="5">
+        <v>77</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="C82" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="D80" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E80" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="F80" s="5" t="s">
+      <c r="D82" s="6" t="s">
         <v>458</v>
       </c>
-      <c r="G80" s="29">
+      <c r="E82" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="G82" s="29">
         <v>1</v>
       </c>
-      <c r="H80" s="6" t="s">
-        <v>398</v>
+      <c r="H82" s="6" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="5">
+        <v>78</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="G83" s="29">
+        <v>4</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="5">
+        <v>79</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="G84" s="29">
+        <v>4</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="5">
+        <v>80</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="G85" s="29">
+        <v>4</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="5">
+        <v>81</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="G86" s="29">
+        <v>8</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="5">
+        <v>82</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="G87" s="29">
+        <v>3</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="5">
+        <v>83</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="G88" s="29">
+        <v>3</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="5">
+        <v>84</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="G89" s="29">
+        <v>1</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="5">
+        <v>85</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="G90" s="29">
+        <v>40</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="5">
+        <v>86</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="G91" s="29">
+        <v>5</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="5">
+        <v>87</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="G92" s="29">
+        <v>1</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>399</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:H80"/>
+  <autoFilter ref="A5:H92"/>
   <mergeCells count="3">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>

--- a/exemplo/quadro-de-cargas-residencia-unifamiliar-exemplo-r00.xlsx
+++ b/exemplo/quadro-de-cargas-residencia-unifamiliar-exemplo-r00.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="477">
   <si>
     <t>Quadro de cargas — QM — Quadro de medição (ponto de entrega)</t>
   </si>
@@ -1164,16 +1164,19 @@
     <t>Dispositivos de proteção</t>
   </si>
   <si>
-    <t>DPS classe I+II — Uc 175 V, Iimp 12,5 kA (10/350 µs), In 20 kA</t>
-  </si>
-  <si>
-    <t>ABNT NBR IEC 61643-11; NBR 5419-4</t>
-  </si>
-  <si>
-    <t>DPS classe II — Uc 175 V, In 20 kA, Imáx 40 kA</t>
+    <t>DPS classe I+II unipolar — Uc 175 V, Iimp 12,5 kA (10/350 µs), In 20 kA, Up ≤ 1,5 kV</t>
   </si>
   <si>
     <t>ABNT NBR IEC 61643-11</t>
+  </si>
+  <si>
+    <t>Condutor de cobre verde-amarelo 16 mm² para ligação dos DPS</t>
+  </si>
+  <si>
+    <t>DPS classe II unipolar — Uc 175 V, In 20 kA, Imáx 40 kA (8/20 µs), Up ≤ 1,2 kV</t>
+  </si>
+  <si>
+    <t>Condutor de cobre verde-amarelo 4 mm² para ligação dos DPS</t>
   </si>
   <si>
     <t>Disjuntor termomagnético 1P curva C 10 A — 6,0 kA</t>
@@ -3244,7 +3247,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -4187,19 +4190,19 @@
         <v>382</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>383</v>
+        <v>340</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="G39" s="29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -4210,10 +4213,10 @@
         <v>379</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>110</v>
@@ -4222,10 +4225,10 @@
         <v>332</v>
       </c>
       <c r="G40" s="29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>386</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -4236,22 +4239,22 @@
         <v>379</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>385</v>
+        <v>340</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="G41" s="29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>388</v>
+        <v>105</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -4262,10 +4265,10 @@
         <v>379</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>110</v>
@@ -4274,10 +4277,10 @@
         <v>332</v>
       </c>
       <c r="G42" s="29">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -4288,10 +4291,10 @@
         <v>379</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>110</v>
@@ -4300,10 +4303,10 @@
         <v>332</v>
       </c>
       <c r="G43" s="29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>64</v>
+        <v>389</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -4314,10 +4317,10 @@
         <v>379</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>110</v>
@@ -4326,10 +4329,10 @@
         <v>332</v>
       </c>
       <c r="G44" s="29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>71</v>
+        <v>391</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -4340,10 +4343,10 @@
         <v>379</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>110</v>
@@ -4355,7 +4358,7 @@
         <v>1</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -4366,10 +4369,10 @@
         <v>379</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>110</v>
@@ -4378,10 +4381,10 @@
         <v>332</v>
       </c>
       <c r="G46" s="29">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>396</v>
+        <v>71</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -4392,10 +4395,10 @@
         <v>379</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>110</v>
@@ -4407,7 +4410,7 @@
         <v>1</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -4418,10 +4421,10 @@
         <v>379</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>110</v>
@@ -4430,10 +4433,10 @@
         <v>332</v>
       </c>
       <c r="G48" s="29">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -4441,13 +4444,13 @@
         <v>44</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>400</v>
+        <v>379</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>110</v>
@@ -4459,7 +4462,7 @@
         <v>1</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -4467,13 +4470,13 @@
         <v>45</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>400</v>
+        <v>379</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>402</v>
+        <v>381</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>110</v>
@@ -4482,10 +4485,10 @@
         <v>332</v>
       </c>
       <c r="G50" s="29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -4493,13 +4496,13 @@
         <v>46</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>110</v>
@@ -4511,7 +4514,7 @@
         <v>1</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>399</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -4519,25 +4522,25 @@
         <v>47</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="G52" s="29">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -4545,25 +4548,25 @@
         <v>48</v>
       </c>
       <c r="B53" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="C53" s="6" t="s">
         <v>405</v>
       </c>
-      <c r="C53" s="6" t="s">
-        <v>409</v>
-      </c>
       <c r="D53" s="6" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="G53" s="29">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -4571,13 +4574,13 @@
         <v>49</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>110</v>
@@ -4586,10 +4589,10 @@
         <v>341</v>
       </c>
       <c r="G54" s="29">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -4597,13 +4600,13 @@
         <v>50</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>110</v>
@@ -4612,10 +4615,10 @@
         <v>341</v>
       </c>
       <c r="G55" s="29">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -4623,13 +4626,13 @@
         <v>51</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>110</v>
@@ -4638,10 +4641,10 @@
         <v>341</v>
       </c>
       <c r="G56" s="29">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -4649,25 +4652,25 @@
         <v>52</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="G57" s="29">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -4675,25 +4678,25 @@
         <v>53</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="G58" s="29">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -4701,13 +4704,13 @@
         <v>54</v>
       </c>
       <c r="B59" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="C59" s="6" t="s">
         <v>419</v>
       </c>
-      <c r="C59" s="6" t="s">
-        <v>422</v>
-      </c>
       <c r="D59" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>110</v>
@@ -4716,10 +4719,10 @@
         <v>332</v>
       </c>
       <c r="G59" s="29">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -4727,13 +4730,13 @@
         <v>55</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>110</v>
@@ -4742,10 +4745,10 @@
         <v>332</v>
       </c>
       <c r="G60" s="29">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -4753,13 +4756,13 @@
         <v>56</v>
       </c>
       <c r="B61" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="C61" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="C61" s="6" t="s">
-        <v>426</v>
-      </c>
       <c r="D61" s="6" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E61" s="6" t="s">
         <v>110</v>
@@ -4768,10 +4771,10 @@
         <v>332</v>
       </c>
       <c r="G61" s="29">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -4779,13 +4782,13 @@
         <v>57</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>110</v>
@@ -4794,10 +4797,10 @@
         <v>332</v>
       </c>
       <c r="G62" s="29">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -4805,13 +4808,13 @@
         <v>58</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>110</v>
@@ -4820,10 +4823,10 @@
         <v>332</v>
       </c>
       <c r="G63" s="29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -4831,13 +4834,13 @@
         <v>59</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>110</v>
@@ -4846,10 +4849,10 @@
         <v>332</v>
       </c>
       <c r="G64" s="29">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -4857,13 +4860,13 @@
         <v>60</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>44</v>
+        <v>424</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>110</v>
@@ -4872,10 +4875,10 @@
         <v>332</v>
       </c>
       <c r="G65" s="29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>186</v>
+        <v>400</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -4883,13 +4886,13 @@
         <v>61</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>44</v>
+        <v>424</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>110</v>
@@ -4898,10 +4901,10 @@
         <v>332</v>
       </c>
       <c r="G66" s="29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>190</v>
+        <v>400</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -4912,10 +4915,10 @@
         <v>44</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E67" s="6" t="s">
         <v>110</v>
@@ -4924,10 +4927,10 @@
         <v>332</v>
       </c>
       <c r="G67" s="29">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -4938,10 +4941,10 @@
         <v>44</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>110</v>
@@ -4950,10 +4953,10 @@
         <v>332</v>
       </c>
       <c r="G68" s="29">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -4964,10 +4967,10 @@
         <v>44</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>110</v>
@@ -4976,10 +4979,10 @@
         <v>332</v>
       </c>
       <c r="G69" s="29">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -4990,10 +4993,10 @@
         <v>44</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>110</v>
@@ -5002,10 +5005,10 @@
         <v>332</v>
       </c>
       <c r="G70" s="29">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -5016,10 +5019,10 @@
         <v>44</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>110</v>
@@ -5028,7 +5031,7 @@
         <v>332</v>
       </c>
       <c r="G71" s="29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>218</v>
@@ -5039,25 +5042,25 @@
         <v>67</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>442</v>
+        <v>44</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="G72" s="29">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>445</v>
+        <v>218</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -5065,25 +5068,25 @@
         <v>68</v>
       </c>
       <c r="B73" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="D73" s="6" t="s">
         <v>442</v>
       </c>
-      <c r="C73" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>444</v>
-      </c>
       <c r="E73" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="G73" s="29">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>445</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -5091,13 +5094,13 @@
         <v>69</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>110</v>
@@ -5106,10 +5109,10 @@
         <v>341</v>
       </c>
       <c r="G74" s="29">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -5117,25 +5120,25 @@
         <v>70</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E75" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="G75" s="29">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -5143,25 +5146,25 @@
         <v>71</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="G76" s="29">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -5169,13 +5172,13 @@
         <v>72</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>110</v>
@@ -5184,10 +5187,10 @@
         <v>332</v>
       </c>
       <c r="G77" s="29">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -5195,13 +5198,13 @@
         <v>73</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>110</v>
@@ -5210,10 +5213,10 @@
         <v>332</v>
       </c>
       <c r="G78" s="29">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -5221,25 +5224,25 @@
         <v>74</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>407</v>
+        <v>445</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="G79" s="29">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -5247,13 +5250,13 @@
         <v>75</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>110</v>
@@ -5265,7 +5268,7 @@
         <v>4</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -5273,25 +5276,25 @@
         <v>76</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>456</v>
+        <v>408</v>
       </c>
       <c r="E81" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="G81" s="29">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -5299,25 +5302,25 @@
         <v>77</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="G82" s="29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -5325,13 +5328,13 @@
         <v>78</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="E83" s="6" t="s">
         <v>110</v>
@@ -5343,7 +5346,7 @@
         <v>4</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -5351,25 +5354,25 @@
         <v>79</v>
       </c>
       <c r="B84" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="D84" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="C84" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>456</v>
-      </c>
       <c r="E84" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="G84" s="29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -5377,13 +5380,13 @@
         <v>80</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>110</v>
+        <v>462</v>
       </c>
       <c r="E85" s="6" t="s">
         <v>110</v>
@@ -5395,7 +5398,7 @@
         <v>4</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -5403,25 +5406,25 @@
         <v>81</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="G86" s="29">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
@@ -5429,25 +5432,25 @@
         <v>82</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>456</v>
+        <v>110</v>
       </c>
       <c r="E87" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="G87" s="29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -5455,13 +5458,13 @@
         <v>83</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>407</v>
+        <v>457</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>110</v>
@@ -5470,10 +5473,10 @@
         <v>341</v>
       </c>
       <c r="G88" s="29">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -5481,25 +5484,25 @@
         <v>84</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="E89" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="G89" s="29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>399</v>
+        <v>463</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -5507,25 +5510,25 @@
         <v>85</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>110</v>
+        <v>408</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="G90" s="29">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>399</v>
+        <v>463</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -5533,25 +5536,25 @@
         <v>86</v>
       </c>
       <c r="B91" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="D91" s="6" t="s">
         <v>470</v>
       </c>
-      <c r="C91" s="6" t="s">
-        <v>472</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>110</v>
-      </c>
       <c r="E91" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>473</v>
+        <v>332</v>
       </c>
       <c r="G91" s="29">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -5559,29 +5562,81 @@
         <v>87</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C92" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="G92" s="29">
+        <v>40</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="5">
+        <v>88</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F93" s="5" t="s">
         <v>474</v>
       </c>
-      <c r="D92" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E92" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="F92" s="5" t="s">
+      <c r="G93" s="29">
+        <v>5</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="5">
+        <v>89</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="C94" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="G92" s="29">
+      <c r="D94" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="G94" s="29">
         <v>1</v>
       </c>
-      <c r="H92" s="6" t="s">
-        <v>399</v>
+      <c r="H94" s="6" t="s">
+        <v>400</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:H92"/>
+  <autoFilter ref="A5:H94"/>
   <mergeCells count="3">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>

--- a/exemplo/quadro-de-cargas-residencia-unifamiliar-exemplo-r00.xlsx
+++ b/exemplo/quadro-de-cargas-residencia-unifamiliar-exemplo-r00.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="479">
   <si>
     <t>Quadro de cargas — QM — Quadro de medição (ponto de entrega)</t>
   </si>
@@ -1164,7 +1164,7 @@
     <t>Dispositivos de proteção</t>
   </si>
   <si>
-    <t>DPS classe I+II unipolar — Uc 175 V, Iimp 12,5 kA (10/350 µs), In 20 kA, Up ≤ 1,5 kV</t>
+    <t>DPS classe I+II unipolar (varistor) — Uc 175 V, Iimp 12,5 kA (10/350 µs), In 20 kA, Up ≤ 1,5 kV</t>
   </si>
   <si>
     <t>ABNT NBR IEC 61643-11</t>
@@ -1177,6 +1177,12 @@
   </si>
   <si>
     <t>Condutor de cobre verde-amarelo 4 mm² para ligação dos DPS</t>
+  </si>
+  <si>
+    <t>DPS classe III junto ao equipamento sensível — Uc 175 V</t>
+  </si>
+  <si>
+    <t>equipamentos sensíveis</t>
   </si>
   <si>
     <t>Disjuntor termomagnético 1P curva C 10 A — 6,0 kA</t>
@@ -3247,7 +3253,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -4268,7 +4274,7 @@
         <v>385</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>110</v>
@@ -4277,10 +4283,10 @@
         <v>332</v>
       </c>
       <c r="G42" s="29">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -4291,10 +4297,10 @@
         <v>379</v>
       </c>
       <c r="C43" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="D43" s="6" t="s">
         <v>388</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>386</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>110</v>
@@ -4303,7 +4309,7 @@
         <v>332</v>
       </c>
       <c r="G43" s="29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>389</v>
@@ -4320,7 +4326,7 @@
         <v>390</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>110</v>
@@ -4329,7 +4335,7 @@
         <v>332</v>
       </c>
       <c r="G44" s="29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>391</v>
@@ -4346,7 +4352,7 @@
         <v>392</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>110</v>
@@ -4355,10 +4361,10 @@
         <v>332</v>
       </c>
       <c r="G45" s="29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>64</v>
+        <v>393</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -4369,10 +4375,10 @@
         <v>379</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>110</v>
@@ -4384,7 +4390,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -4395,10 +4401,10 @@
         <v>379</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>110</v>
@@ -4410,7 +4416,7 @@
         <v>1</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -4421,10 +4427,10 @@
         <v>379</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>110</v>
@@ -4433,10 +4439,10 @@
         <v>332</v>
       </c>
       <c r="G48" s="29">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>397</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -4447,10 +4453,10 @@
         <v>379</v>
       </c>
       <c r="C49" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="D49" s="6" t="s">
         <v>398</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>396</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>110</v>
@@ -4459,10 +4465,10 @@
         <v>332</v>
       </c>
       <c r="G49" s="29">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>71</v>
+        <v>399</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -4473,10 +4479,10 @@
         <v>379</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>381</v>
+        <v>398</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>110</v>
@@ -4485,10 +4491,10 @@
         <v>332</v>
       </c>
       <c r="G50" s="29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>400</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -4496,13 +4502,13 @@
         <v>46</v>
       </c>
       <c r="B51" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="C51" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="C51" s="6" t="s">
-        <v>402</v>
-      </c>
       <c r="D51" s="6" t="s">
-        <v>403</v>
+        <v>381</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>110</v>
@@ -4511,10 +4517,10 @@
         <v>332</v>
       </c>
       <c r="G51" s="29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>105</v>
+        <v>402</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -4522,13 +4528,13 @@
         <v>47</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>404</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>110</v>
@@ -4540,7 +4546,7 @@
         <v>1</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>400</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -4548,13 +4554,13 @@
         <v>48</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C53" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="D53" s="6" t="s">
         <v>405</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>403</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>110</v>
@@ -4566,7 +4572,7 @@
         <v>1</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -4574,25 +4580,25 @@
         <v>49</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>407</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="G54" s="29">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -4600,13 +4606,13 @@
         <v>50</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C55" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="D55" s="6" t="s">
         <v>410</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>408</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>110</v>
@@ -4615,7 +4621,7 @@
         <v>341</v>
       </c>
       <c r="G55" s="29">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>411</v>
@@ -4626,13 +4632,13 @@
         <v>51</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>412</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>110</v>
@@ -4641,7 +4647,7 @@
         <v>341</v>
       </c>
       <c r="G56" s="29">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="H56" s="6" t="s">
         <v>413</v>
@@ -4652,13 +4658,13 @@
         <v>52</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>414</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>110</v>
@@ -4667,7 +4673,7 @@
         <v>341</v>
       </c>
       <c r="G57" s="29">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>415</v>
@@ -4678,13 +4684,13 @@
         <v>53</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>416</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>110</v>
@@ -4696,7 +4702,7 @@
         <v>14</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -4704,25 +4710,25 @@
         <v>54</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C59" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="D59" s="6" t="s">
         <v>419</v>
       </c>
-      <c r="D59" s="6" t="s">
-        <v>417</v>
-      </c>
       <c r="E59" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="G59" s="29">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -4730,13 +4736,13 @@
         <v>55</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>421</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>110</v>
@@ -4745,10 +4751,10 @@
         <v>332</v>
       </c>
       <c r="G60" s="29">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -4756,13 +4762,13 @@
         <v>56</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>423</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E61" s="6" t="s">
         <v>110</v>
@@ -4771,10 +4777,10 @@
         <v>332</v>
       </c>
       <c r="G61" s="29">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -4782,13 +4788,13 @@
         <v>57</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>425</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>110</v>
@@ -4797,10 +4803,10 @@
         <v>332</v>
       </c>
       <c r="G62" s="29">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -4808,13 +4814,13 @@
         <v>58</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>427</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>110</v>
@@ -4823,10 +4829,10 @@
         <v>332</v>
       </c>
       <c r="G63" s="29">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -4834,13 +4840,13 @@
         <v>59</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C64" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="D64" s="6" t="s">
         <v>428</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>429</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>110</v>
@@ -4849,10 +4855,10 @@
         <v>332</v>
       </c>
       <c r="G64" s="29">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -4860,13 +4866,13 @@
         <v>60</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>430</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>110</v>
@@ -4875,10 +4881,10 @@
         <v>332</v>
       </c>
       <c r="G65" s="29">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -4886,13 +4892,13 @@
         <v>61</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C66" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="D66" s="6" t="s">
         <v>431</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>422</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>110</v>
@@ -4901,10 +4907,10 @@
         <v>332</v>
       </c>
       <c r="G66" s="29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -4912,13 +4918,13 @@
         <v>62</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>44</v>
+        <v>426</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="E67" s="6" t="s">
         <v>110</v>
@@ -4927,10 +4933,10 @@
         <v>332</v>
       </c>
       <c r="G67" s="29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>186</v>
+        <v>402</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -4944,7 +4950,7 @@
         <v>434</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>110</v>
@@ -4956,7 +4962,7 @@
         <v>4</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -4967,10 +4973,10 @@
         <v>44</v>
       </c>
       <c r="C69" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="D69" s="6" t="s">
         <v>435</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>433</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>110</v>
@@ -4979,10 +4985,10 @@
         <v>332</v>
       </c>
       <c r="G69" s="29">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -4993,10 +4999,10 @@
         <v>44</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>110</v>
@@ -5005,10 +5011,10 @@
         <v>332</v>
       </c>
       <c r="G70" s="29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -5019,10 +5025,10 @@
         <v>44</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>110</v>
@@ -5031,10 +5037,10 @@
         <v>332</v>
       </c>
       <c r="G71" s="29">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -5083,7 +5089,7 @@
         <v>332</v>
       </c>
       <c r="G73" s="29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>218</v>
@@ -5094,25 +5100,25 @@
         <v>69</v>
       </c>
       <c r="B74" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C74" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="C74" s="6" t="s">
+      <c r="D74" s="6" t="s">
         <v>444</v>
       </c>
-      <c r="D74" s="6" t="s">
-        <v>445</v>
-      </c>
       <c r="E74" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="G74" s="29">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>446</v>
+        <v>218</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -5120,13 +5126,13 @@
         <v>70</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C75" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="D75" s="6" t="s">
         <v>447</v>
-      </c>
-      <c r="D75" s="6" t="s">
-        <v>445</v>
       </c>
       <c r="E75" s="6" t="s">
         <v>110</v>
@@ -5135,10 +5141,10 @@
         <v>341</v>
       </c>
       <c r="G75" s="29">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -5146,13 +5152,13 @@
         <v>71</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>110</v>
@@ -5161,10 +5167,10 @@
         <v>341</v>
       </c>
       <c r="G76" s="29">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -5172,25 +5178,25 @@
         <v>72</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>450</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="G77" s="29">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -5198,13 +5204,13 @@
         <v>73</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>110</v>
@@ -5213,10 +5219,10 @@
         <v>332</v>
       </c>
       <c r="G78" s="29">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -5224,13 +5230,13 @@
         <v>74</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>110</v>
@@ -5239,10 +5245,10 @@
         <v>332</v>
       </c>
       <c r="G79" s="29">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -5250,13 +5256,13 @@
         <v>75</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>110</v>
@@ -5268,7 +5274,7 @@
         <v>4</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -5276,25 +5282,25 @@
         <v>76</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="E81" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="G81" s="29">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -5302,25 +5308,25 @@
         <v>77</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>445</v>
+        <v>410</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="G82" s="29">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -5328,13 +5334,13 @@
         <v>78</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="E83" s="6" t="s">
         <v>110</v>
@@ -5346,7 +5352,7 @@
         <v>4</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -5354,7 +5360,7 @@
         <v>79</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>458</v>
@@ -5366,13 +5372,13 @@
         <v>110</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="G84" s="29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -5380,25 +5386,25 @@
         <v>80</v>
       </c>
       <c r="B85" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="C85" s="6" t="s">
         <v>460</v>
       </c>
-      <c r="C85" s="6" t="s">
+      <c r="D85" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="D85" s="6" t="s">
-        <v>462</v>
-      </c>
       <c r="E85" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="G85" s="29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>463</v>
+        <v>448</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -5406,13 +5412,13 @@
         <v>81</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C86" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="D86" s="6" t="s">
         <v>464</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>457</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>110</v>
@@ -5424,7 +5430,7 @@
         <v>4</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
@@ -5432,13 +5438,13 @@
         <v>82</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>110</v>
+        <v>459</v>
       </c>
       <c r="E87" s="6" t="s">
         <v>110</v>
@@ -5450,7 +5456,7 @@
         <v>4</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -5458,25 +5464,25 @@
         <v>83</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>457</v>
+        <v>110</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="G88" s="29">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -5484,13 +5490,13 @@
         <v>84</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E89" s="6" t="s">
         <v>110</v>
@@ -5499,10 +5505,10 @@
         <v>341</v>
       </c>
       <c r="G89" s="29">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -5510,13 +5516,13 @@
         <v>85</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>408</v>
+        <v>459</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>110</v>
@@ -5528,7 +5534,7 @@
         <v>3</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -5536,25 +5542,25 @@
         <v>86</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>470</v>
+        <v>410</v>
       </c>
       <c r="E91" s="6" t="s">
         <v>110</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="G91" s="29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>400</v>
+        <v>465</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -5562,13 +5568,13 @@
         <v>87</v>
       </c>
       <c r="B92" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="C92" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="C92" s="6" t="s">
+      <c r="D92" s="6" t="s">
         <v>472</v>
-      </c>
-      <c r="D92" s="6" t="s">
-        <v>110</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>110</v>
@@ -5577,10 +5583,10 @@
         <v>332</v>
       </c>
       <c r="G92" s="29">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -5588,10 +5594,10 @@
         <v>88</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>110</v>
@@ -5600,13 +5606,13 @@
         <v>110</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>474</v>
+        <v>332</v>
       </c>
       <c r="G93" s="29">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -5614,7 +5620,7 @@
         <v>89</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>475</v>
@@ -5629,14 +5635,40 @@
         <v>476</v>
       </c>
       <c r="G94" s="29">
+        <v>5</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="5">
+        <v>90</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F95" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G95" s="29">
         <v>1</v>
       </c>
-      <c r="H94" s="6" t="s">
-        <v>400</v>
+      <c r="H95" s="6" t="s">
+        <v>402</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:H94"/>
+  <autoFilter ref="A5:H95"/>
   <mergeCells count="3">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>

--- a/exemplo/quadro-de-cargas-residencia-unifamiliar-exemplo-r00.xlsx
+++ b/exemplo/quadro-de-cargas-residencia-unifamiliar-exemplo-r00.xlsx
@@ -1170,13 +1170,13 @@
     <t>ABNT NBR IEC 61643-11</t>
   </si>
   <si>
-    <t>Condutor de cobre verde-amarelo 16 mm² para ligação dos DPS</t>
+    <t>Condutor de cobre 16 mm² para ligação dos DPS (fases e PE)</t>
   </si>
   <si>
     <t>DPS classe II unipolar — Uc 175 V, In 20 kA, Imáx 40 kA (8/20 µs), Up ≤ 1,2 kV</t>
   </si>
   <si>
-    <t>Condutor de cobre verde-amarelo 4 mm² para ligação dos DPS</t>
+    <t>Condutor de cobre 10 mm² para ligação dos DPS (fases e PE)</t>
   </si>
   <si>
     <t>DPS classe III junto ao equipamento sensível — Uc 175 V</t>

--- a/exemplo/quadro-de-cargas-residencia-unifamiliar-exemplo-r00.xlsx
+++ b/exemplo/quadro-de-cargas-residencia-unifamiliar-exemplo-r00.xlsx
@@ -30,7 +30,7 @@
     <t>Obra: Residência unifamiliar — exemplo — Proprietário (exemplo)</t>
   </si>
   <si>
-    <t>Sistema: 127/220 V, trifásico, esquema TN-S · Responsável: Nome do responsável técnico — CREA/CFT nº 000000 · R00 · 27/10/2026</t>
+    <t>Sistema: 127/220 V, trifásico, esquema TN-S · Responsável: Nome do responsável técnico — CREA/CFT nº 000000 · R00 · 28/10/2026</t>
   </si>
   <si>
     <t>Circ.</t>
@@ -1164,12 +1164,15 @@
     <t>Dispositivos de proteção</t>
   </si>
   <si>
-    <t>DPS classe I+II unipolar (varistor) — Uc 175 V, Iimp 12,5 kA (10/350 µs), In 20 kA, Up ≤ 1,5 kV</t>
+    <t>Conjunto de DPS classe I+II 4+0 — Uc 275 V, Iimp 12,5 kA (10/350 µs), In 30 kA, Up ≤ 1,5 kV — ref. CLAMPER Front V 275 V 12,5/60 kA 4+0 (cód. 026979) ou equivalente</t>
   </si>
   <si>
     <t>ABNT NBR IEC 61643-11</t>
   </si>
   <si>
+    <t>cj</t>
+  </si>
+  <si>
     <t>Condutor de cobre 16 mm² para ligação dos DPS (fases e PE)</t>
   </si>
   <si>
@@ -1456,9 +1459,6 @@
   </si>
   <si>
     <t>Anilhas/etiquetas de identificação de circuitos</t>
-  </si>
-  <si>
-    <t>cj</t>
   </si>
 </sst>
 </file>
@@ -4176,10 +4176,10 @@
         <v>110</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>332</v>
+        <v>382</v>
       </c>
       <c r="G38" s="29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>123</v>
@@ -4193,7 +4193,7 @@
         <v>379</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>340</v>
@@ -4219,7 +4219,7 @@
         <v>379</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>381</v>
@@ -4245,7 +4245,7 @@
         <v>379</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>340</v>
@@ -4271,7 +4271,7 @@
         <v>379</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>381</v>
@@ -4286,7 +4286,7 @@
         <v>2</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -4297,10 +4297,10 @@
         <v>379</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>110</v>
@@ -4312,7 +4312,7 @@
         <v>5</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -4323,10 +4323,10 @@
         <v>379</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>110</v>
@@ -4338,7 +4338,7 @@
         <v>4</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -4349,10 +4349,10 @@
         <v>379</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>110</v>
@@ -4364,7 +4364,7 @@
         <v>2</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -4375,10 +4375,10 @@
         <v>379</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>110</v>
@@ -4401,10 +4401,10 @@
         <v>379</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>110</v>
@@ -4427,10 +4427,10 @@
         <v>379</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>110</v>
@@ -4453,10 +4453,10 @@
         <v>379</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>110</v>
@@ -4468,7 +4468,7 @@
         <v>9</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -4479,10 +4479,10 @@
         <v>379</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>110</v>
@@ -4505,7 +4505,7 @@
         <v>379</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>381</v>
@@ -4520,7 +4520,7 @@
         <v>4</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -4528,13 +4528,13 @@
         <v>47</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>110</v>
@@ -4554,13 +4554,13 @@
         <v>48</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C53" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="D53" s="6" t="s">
         <v>406</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>405</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>110</v>
@@ -4572,7 +4572,7 @@
         <v>1</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -4580,13 +4580,13 @@
         <v>49</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>110</v>
@@ -4598,7 +4598,7 @@
         <v>1</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -4606,13 +4606,13 @@
         <v>50</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>110</v>
@@ -4624,7 +4624,7 @@
         <v>51</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -4632,13 +4632,13 @@
         <v>51</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>110</v>
@@ -4650,7 +4650,7 @@
         <v>9</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -4658,13 +4658,13 @@
         <v>52</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>110</v>
@@ -4676,7 +4676,7 @@
         <v>39</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -4684,13 +4684,13 @@
         <v>53</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>110</v>
@@ -4702,7 +4702,7 @@
         <v>14</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -4710,13 +4710,13 @@
         <v>54</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>110</v>
@@ -4728,7 +4728,7 @@
         <v>14</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -4736,13 +4736,13 @@
         <v>55</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>110</v>
@@ -4754,7 +4754,7 @@
         <v>9</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -4762,13 +4762,13 @@
         <v>56</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E61" s="6" t="s">
         <v>110</v>
@@ -4780,7 +4780,7 @@
         <v>30</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -4788,13 +4788,13 @@
         <v>57</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C62" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="D62" s="6" t="s">
         <v>425</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>424</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>110</v>
@@ -4806,7 +4806,7 @@
         <v>14</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -4814,13 +4814,13 @@
         <v>58</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>110</v>
@@ -4832,7 +4832,7 @@
         <v>18</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -4840,13 +4840,13 @@
         <v>59</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C64" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="D64" s="6" t="s">
         <v>429</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>428</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>110</v>
@@ -4858,7 +4858,7 @@
         <v>4</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -4866,13 +4866,13 @@
         <v>60</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>110</v>
@@ -4884,7 +4884,7 @@
         <v>8</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -4892,13 +4892,13 @@
         <v>61</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C66" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="D66" s="6" t="s">
         <v>432</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>431</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>110</v>
@@ -4910,7 +4910,7 @@
         <v>2</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -4918,13 +4918,13 @@
         <v>62</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E67" s="6" t="s">
         <v>110</v>
@@ -4936,7 +4936,7 @@
         <v>3</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -4947,10 +4947,10 @@
         <v>44</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>110</v>
@@ -4973,10 +4973,10 @@
         <v>44</v>
       </c>
       <c r="C69" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="D69" s="6" t="s">
         <v>436</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>435</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>110</v>
@@ -4999,10 +4999,10 @@
         <v>44</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>110</v>
@@ -5025,10 +5025,10 @@
         <v>44</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>110</v>
@@ -5051,10 +5051,10 @@
         <v>44</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>110</v>
@@ -5077,10 +5077,10 @@
         <v>44</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E73" s="6" t="s">
         <v>110</v>
@@ -5103,10 +5103,10 @@
         <v>44</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>110</v>
@@ -5126,13 +5126,13 @@
         <v>70</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E75" s="6" t="s">
         <v>110</v>
@@ -5144,7 +5144,7 @@
         <v>49</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -5152,13 +5152,13 @@
         <v>71</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>110</v>
@@ -5170,7 +5170,7 @@
         <v>28</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -5178,13 +5178,13 @@
         <v>72</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>110</v>
@@ -5196,7 +5196,7 @@
         <v>63</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -5204,13 +5204,13 @@
         <v>73</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>110</v>
@@ -5222,7 +5222,7 @@
         <v>46</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -5230,13 +5230,13 @@
         <v>74</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>110</v>
@@ -5248,7 +5248,7 @@
         <v>24</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -5256,13 +5256,13 @@
         <v>75</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>110</v>
@@ -5274,7 +5274,7 @@
         <v>4</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -5282,13 +5282,13 @@
         <v>76</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E81" s="6" t="s">
         <v>110</v>
@@ -5300,7 +5300,7 @@
         <v>4</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -5308,13 +5308,13 @@
         <v>77</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>110</v>
@@ -5326,7 +5326,7 @@
         <v>10</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -5334,13 +5334,13 @@
         <v>78</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E83" s="6" t="s">
         <v>110</v>
@@ -5352,7 +5352,7 @@
         <v>4</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -5360,13 +5360,13 @@
         <v>79</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>110</v>
@@ -5378,7 +5378,7 @@
         <v>4</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -5386,13 +5386,13 @@
         <v>80</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E85" s="6" t="s">
         <v>110</v>
@@ -5404,7 +5404,7 @@
         <v>1</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -5412,13 +5412,13 @@
         <v>81</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>110</v>
@@ -5430,7 +5430,7 @@
         <v>4</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
@@ -5438,13 +5438,13 @@
         <v>82</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E87" s="6" t="s">
         <v>110</v>
@@ -5456,7 +5456,7 @@
         <v>4</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -5464,10 +5464,10 @@
         <v>83</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>110</v>
@@ -5482,7 +5482,7 @@
         <v>4</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -5490,13 +5490,13 @@
         <v>84</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E89" s="6" t="s">
         <v>110</v>
@@ -5508,7 +5508,7 @@
         <v>8</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -5516,13 +5516,13 @@
         <v>85</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>110</v>
@@ -5534,7 +5534,7 @@
         <v>3</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -5542,13 +5542,13 @@
         <v>86</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E91" s="6" t="s">
         <v>110</v>
@@ -5560,7 +5560,7 @@
         <v>3</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -5568,13 +5568,13 @@
         <v>87</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>110</v>
@@ -5586,7 +5586,7 @@
         <v>1</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -5594,10 +5594,10 @@
         <v>88</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>110</v>
@@ -5612,7 +5612,7 @@
         <v>40</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -5620,10 +5620,10 @@
         <v>89</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>110</v>
@@ -5632,13 +5632,13 @@
         <v>110</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G94" s="29">
         <v>5</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -5646,10 +5646,10 @@
         <v>90</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D95" s="6" t="s">
         <v>110</v>
@@ -5658,13 +5658,13 @@
         <v>110</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>478</v>
+        <v>382</v>
       </c>
       <c r="G95" s="29">
         <v>1</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
